--- a/English Premier League/X_pred.xlsx
+++ b/English Premier League/X_pred.xlsx
@@ -1547,13 +1547,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1586,19 +1586,19 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1616,85 +1616,85 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1703,16 +1703,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
         <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>1</v>
@@ -1721,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
         <v>1</v>
@@ -1739,103 +1739,103 @@
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.427586206896552</v>
+        <v>4.43448275862069</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.313103448275863</v>
+        <v>6.720000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>42.50482758620691</v>
+        <v>49.056</v>
       </c>
       <c r="BP2" t="n">
-        <v>11.21655172413793</v>
+        <v>15.456</v>
       </c>
       <c r="BQ2" t="n">
-        <v>157.0317241379311</v>
+        <v>218.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>31.87862068965518</v>
+        <v>30.24</v>
       </c>
       <c r="BS2" t="n">
-        <v>18.89103448275862</v>
+        <v>22.848</v>
       </c>
       <c r="BT2" t="n">
-        <v>53.72137931034484</v>
+        <v>75.264</v>
       </c>
       <c r="BU2" t="n">
-        <v>1766.902068965518</v>
+        <v>2368.128</v>
       </c>
       <c r="BV2" t="n">
-        <v>46.63724137931035</v>
+        <v>46.36800000000001</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.34896551724138</v>
+        <v>21.504</v>
       </c>
       <c r="BX2" t="n">
-        <v>38.37241379310345</v>
+        <v>65.184</v>
       </c>
       <c r="BY2" t="n">
-        <v>67.88965517241381</v>
+        <v>94.75200000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.771034482758621</v>
+        <v>3.36</v>
       </c>
       <c r="CA2" t="n">
-        <v>11.80689655172414</v>
+        <v>18.816</v>
       </c>
       <c r="CB2" t="n">
-        <v>53.72137931034484</v>
+        <v>68.544</v>
       </c>
       <c r="CC2" t="n">
-        <v>160.5737931034483</v>
+        <v>222.432</v>
       </c>
       <c r="CD2" t="n">
-        <v>1426.863448275862</v>
+        <v>1977.024</v>
       </c>
       <c r="CE2" t="n">
-        <v>1192.496551724138</v>
+        <v>1632.96</v>
       </c>
       <c r="CF2" t="n">
-        <v>242.3955862068966</v>
+        <v>276.9984000000001</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.3397544365072366</v>
+        <v>0.6931865047233469</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.7658057602214936</v>
+        <v>1.336822672064777</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1499288451012589</v>
+        <v>0.3528000000000001</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.9609075981489774</v>
+        <v>0.8842909090909091</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1106497793276312</v>
+        <v>0.1164324283219987</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.3675405564020635</v>
+        <v>0.398330597346756</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.423955862068966</v>
+        <v>2.769984</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.541952861952862</v>
+        <v>1.932426937759585</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1509580728658485</v>
+        <v>0.2281883534389532</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.571771209408379</v>
+        <v>2.180583202543376</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.563697670558148</v>
+        <v>2.069248653568654</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1524351125065636</v>
+        <v>0.1516979076668574</v>
       </c>
       <c r="CS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
@@ -1844,31 +1844,31 @@
         <v>1</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
       </c>
       <c r="DA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC2" t="n">
         <v>1</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE2" t="n">
         <v>1</v>
@@ -1877,34 +1877,34 @@
         <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK2" t="n">
         <v>1</v>
       </c>
       <c r="DL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="DS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>1</v>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
         <v>1</v>
@@ -1934,13 +1934,13 @@
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA2" t="n">
         <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
@@ -1949,13 +1949,13 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>1</v>
       </c>
       <c r="EG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>1</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN2" t="n">
         <v>1</v>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>1</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
         <v>1</v>
@@ -2027,210 +2027,210 @@
         <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>3.137931034482758</v>
+        <v>3.006896551724138</v>
       </c>
       <c r="FF2" t="n">
-        <v>3.631448275862069</v>
+        <v>3.624827586206896</v>
       </c>
       <c r="FG2" t="n">
-        <v>30.86731034482758</v>
+        <v>37.45655172413793</v>
       </c>
       <c r="FH2" t="n">
-        <v>9.683862068965517</v>
+        <v>9.666206896551724</v>
       </c>
       <c r="FI2" t="n">
-        <v>158.5732413793103</v>
+        <v>129.2855172413793</v>
       </c>
       <c r="FJ2" t="n">
-        <v>29.6568275862069</v>
+        <v>30.81103448275862</v>
       </c>
       <c r="FK2" t="n">
-        <v>18.76248275862069</v>
+        <v>11.47862068965517</v>
       </c>
       <c r="FL2" t="n">
-        <v>84.12855172413794</v>
+        <v>41.68551724137931</v>
       </c>
       <c r="FM2" t="n">
-        <v>1840.539034482759</v>
+        <v>1542.364137931035</v>
       </c>
       <c r="FN2" t="n">
-        <v>54.47172413793103</v>
+        <v>50.14344827586207</v>
       </c>
       <c r="FO2" t="n">
-        <v>27.23586206896552</v>
+        <v>27.18620689655172</v>
       </c>
       <c r="FP2" t="n">
-        <v>41.15641379310345</v>
+        <v>65.85103448275862</v>
       </c>
       <c r="FQ2" t="n">
-        <v>75.04993103448277</v>
+        <v>81.55862068965517</v>
       </c>
       <c r="FR2" t="n">
-        <v>6.657655172413794</v>
+        <v>3.020689655172414</v>
       </c>
       <c r="FS2" t="n">
-        <v>19.97296551724138</v>
+        <v>30.20689655172414</v>
       </c>
       <c r="FT2" t="n">
-        <v>59.91889655172414</v>
+        <v>59.80965517241379</v>
       </c>
       <c r="FU2" t="n">
-        <v>185.8091034482759</v>
+        <v>218.0937931034483</v>
       </c>
       <c r="FV2" t="n">
-        <v>1503.419586206897</v>
+        <v>1186.526896551724</v>
       </c>
       <c r="FW2" t="n">
-        <v>1197.167448275862</v>
+        <v>898.9572413793104</v>
       </c>
       <c r="FX2" t="n">
-        <v>239.6755862068966</v>
+        <v>228.8474482758621</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.353363148728666</v>
+        <v>0.3342373488580385</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.9310935562521769</v>
+        <v>0.8120555306762203</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.4466711947056775</v>
+        <v>0.1308965517241379</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.213157436433298</v>
+        <v>0.7123581570559258</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.1698863221429156</v>
+        <v>0.1071672349429493</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3867345132920047</v>
+        <v>0.5623713765488063</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.396755862068966</v>
+        <v>2.28847448275862</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.516292237698098</v>
+        <v>1.721252344187047</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1781171806554555</v>
+        <v>0.1483218597517285</v>
       </c>
       <c r="GH2" t="n">
-        <v>1.59110656255598</v>
+        <v>1.288021315349484</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.575395725678927</v>
+        <v>1.341047408549959</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2088584651740999</v>
+        <v>0.137008745369172</v>
       </c>
       <c r="GK2" t="n">
-        <v>1.681655172413794</v>
+        <v>3.095172413793104</v>
       </c>
       <c r="GL2" t="n">
-        <v>11.63751724137932</v>
+        <v>11.59944827586207</v>
       </c>
       <c r="GM2" t="n">
-        <v>1.532689655172415</v>
+        <v>5.789793103448275</v>
       </c>
       <c r="GN2" t="n">
-        <v>-1.541517241379267</v>
+        <v>89.11448275862074</v>
       </c>
       <c r="GO2" t="n">
-        <v>2.221793103448281</v>
+        <v>-0.5710344827586162</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.1285517241379317</v>
+        <v>11.36937931034483</v>
       </c>
       <c r="GQ2" t="n">
-        <v>-30.4071724137931</v>
+        <v>33.57848275862069</v>
       </c>
       <c r="GR2" t="n">
-        <v>-73.63696551724115</v>
+        <v>825.7638620689656</v>
       </c>
       <c r="GS2" t="n">
-        <v>-7.83448275862068</v>
+        <v>-3.775448275862061</v>
       </c>
       <c r="GT2" t="n">
-        <v>-11.88689655172413</v>
+        <v>-5.682206896551719</v>
       </c>
       <c r="GU2" t="n">
-        <v>-2.783999999999992</v>
+        <v>-0.6670344827586234</v>
       </c>
       <c r="GV2" t="n">
-        <v>-7.160275862068957</v>
+        <v>13.19337931034484</v>
       </c>
       <c r="GW2" t="n">
-        <v>-4.886620689655173</v>
+        <v>0.3393103448275867</v>
       </c>
       <c r="GX2" t="n">
-        <v>-8.166068965517237</v>
+        <v>-11.39089655172414</v>
       </c>
       <c r="GY2" t="n">
-        <v>-6.197517241379302</v>
+        <v>8.734344827586206</v>
       </c>
       <c r="GZ2" t="n">
-        <v>-25.23531034482755</v>
+        <v>4.338206896551782</v>
       </c>
       <c r="HA2" t="n">
-        <v>-76.5561379310343</v>
+        <v>790.497103448276</v>
       </c>
       <c r="HB2" t="n">
-        <v>-4.670896551723899</v>
+        <v>734.0027586206899</v>
       </c>
       <c r="HC2" t="n">
-        <v>2.720000000000056</v>
+        <v>48.150951724138</v>
       </c>
       <c r="HD2" t="n">
-        <v>-0.01360871222142934</v>
+        <v>0.3589491558653083</v>
       </c>
       <c r="HE2" t="n">
-        <v>-0.1652877960306833</v>
+        <v>0.5247671413885571</v>
       </c>
       <c r="HF2" t="n">
-        <v>-0.2967423496044185</v>
+        <v>0.2219034482758621</v>
       </c>
       <c r="HG2" t="n">
-        <v>-0.252249838284321</v>
+        <v>0.1719327520349834</v>
       </c>
       <c r="HH2" t="n">
-        <v>-0.05923654281528437</v>
+        <v>0.009265193379049338</v>
       </c>
       <c r="HI2" t="n">
-        <v>-0.01919395688994119</v>
+        <v>-0.1640407792020503</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.02720000000000011</v>
+        <v>0.4815095172413804</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.02566062425476412</v>
+        <v>0.2111745935725382</v>
       </c>
       <c r="HL2" t="n">
-        <v>-0.02715910778960698</v>
+        <v>0.07986649368722462</v>
       </c>
       <c r="HM2" t="n">
-        <v>-0.01933535314760126</v>
+        <v>0.8925618871938923</v>
       </c>
       <c r="HN2" t="n">
-        <v>-0.0116980551207797</v>
+        <v>0.7282012450186952</v>
       </c>
       <c r="HO2" t="n">
-        <v>-0.05642335266753634</v>
+        <v>0.01468916229768538</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2242,13 +2242,13 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -2287,28 +2287,28 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -2332,16 +2332,16 @@
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -2353,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -2374,19 +2374,19 @@
         <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -2395,115 +2395,115 @@
         <v>1</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.096551724137931</v>
+        <v>3.124137931034483</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.431724137931035</v>
+        <v>5.164137931034483</v>
       </c>
       <c r="BO3" t="n">
-        <v>45.58344827586208</v>
+        <v>38.73103448275862</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.92827586206897</v>
+        <v>13.55586206896552</v>
       </c>
       <c r="BQ3" t="n">
-        <v>153.8441379310345</v>
+        <v>167.1889655172414</v>
       </c>
       <c r="BR3" t="n">
-        <v>43.05103448275862</v>
+        <v>41.95862068965517</v>
       </c>
       <c r="BS3" t="n">
-        <v>18.99310344827586</v>
+        <v>15.49241379310345</v>
       </c>
       <c r="BT3" t="n">
-        <v>62.04413793103449</v>
+        <v>51.64137931034482</v>
       </c>
       <c r="BU3" t="n">
-        <v>1775.855172413793</v>
+        <v>1868.126896551724</v>
       </c>
       <c r="BV3" t="n">
-        <v>53.81379310344828</v>
+        <v>58.74206896551723</v>
       </c>
       <c r="BW3" t="n">
-        <v>24.05793103448276</v>
+        <v>22.59310344827586</v>
       </c>
       <c r="BX3" t="n">
-        <v>43.68413793103449</v>
+        <v>40.66758620689655</v>
       </c>
       <c r="BY3" t="n">
-        <v>89.90068965517241</v>
+        <v>69.71586206896552</v>
       </c>
       <c r="BZ3" t="n">
-        <v>7.597241379310345</v>
+        <v>7.746206896551723</v>
       </c>
       <c r="CA3" t="n">
-        <v>21.52551724137931</v>
+        <v>23.88413793103448</v>
       </c>
       <c r="CB3" t="n">
-        <v>58.87862068965519</v>
+        <v>50.99586206896551</v>
       </c>
       <c r="CC3" t="n">
-        <v>221.5862068965517</v>
+        <v>172.3531034482758</v>
       </c>
       <c r="CD3" t="n">
-        <v>1394.726896551724</v>
+        <v>1513.092413793103</v>
       </c>
       <c r="CE3" t="n">
-        <v>1076.275862068966</v>
+        <v>1233.583448275862</v>
       </c>
       <c r="CF3" t="n">
-        <v>240.0095172413794</v>
+        <v>260.5953103448276</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3459458128078818</v>
+        <v>0.4140438871473354</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.9406108374384236</v>
+        <v>1.149216300940439</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.2915607985480944</v>
+        <v>0.5861352440662785</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.8291433756805808</v>
+        <v>0.9522077922077922</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1455674110569981</v>
+        <v>0.1063318026385561</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.5326101590287923</v>
+        <v>0.3927281846187393</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.400095172413793</v>
+        <v>2.605953103448276</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.481834272660575</v>
+        <v>1.544453912861199</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1712735876657255</v>
+        <v>0.1944240955616869</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.533222284290093</v>
+        <v>1.671953396516889</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.548017925059747</v>
+        <v>1.661735996151047</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1920760784369806</v>
+        <v>0.1383087764424792</v>
       </c>
       <c r="CS3" t="n">
         <v>1</v>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX3" t="n">
         <v>1</v>
@@ -2527,13 +2527,13 @@
         <v>1</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL3" t="n">
         <v>1</v>
@@ -2572,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
         <v>1</v>
@@ -2587,37 +2587,37 @@
         <v>1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
         <v>0</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
@@ -2638,25 +2638,25 @@
         <v>1</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
         <v>1</v>
       </c>
       <c r="EQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
         <v>1</v>
@@ -2665,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU3" t="n">
         <v>1</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
         <v>0</v>
@@ -2689,202 +2689,202 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD3" t="n">
         <v>1</v>
       </c>
       <c r="FE3" t="n">
-        <v>3.124137931034483</v>
+        <v>3.055172413793104</v>
       </c>
       <c r="FF3" t="n">
-        <v>6.990344827586208</v>
+        <v>5.499310344827586</v>
       </c>
       <c r="FG3" t="n">
-        <v>55.22372413793104</v>
+        <v>30.55172413793104</v>
       </c>
       <c r="FH3" t="n">
-        <v>21.67006896551725</v>
+        <v>10.99862068965517</v>
       </c>
       <c r="FI3" t="n">
-        <v>181.0499310344828</v>
+        <v>161.3131034482759</v>
       </c>
       <c r="FJ3" t="n">
-        <v>44.73820689655173</v>
+        <v>38.49517241379311</v>
       </c>
       <c r="FK3" t="n">
-        <v>16.07779310344828</v>
+        <v>14.05379310344827</v>
       </c>
       <c r="FL3" t="n">
-        <v>60.11696551724138</v>
+        <v>57.43724137931035</v>
       </c>
       <c r="FM3" t="n">
-        <v>2071.239172413793</v>
+        <v>1785.44275862069</v>
       </c>
       <c r="FN3" t="n">
-        <v>68.50537931034484</v>
+        <v>49.49379310344828</v>
       </c>
       <c r="FO3" t="n">
-        <v>25.16524137931035</v>
+        <v>15.88689655172414</v>
       </c>
       <c r="FP3" t="n">
-        <v>44.73820689655173</v>
+        <v>37.88413793103449</v>
       </c>
       <c r="FQ3" t="n">
-        <v>60.11696551724138</v>
+        <v>85.54482758620691</v>
       </c>
       <c r="FR3" t="n">
-        <v>9.786482758620691</v>
+        <v>4.888275862068966</v>
       </c>
       <c r="FS3" t="n">
-        <v>27.96137931034483</v>
+        <v>25.05241379310345</v>
       </c>
       <c r="FT3" t="n">
-        <v>53.12662068965518</v>
+        <v>64.15862068965518</v>
       </c>
       <c r="FU3" t="n">
-        <v>175.4576551724138</v>
+        <v>185.1434482758621</v>
       </c>
       <c r="FV3" t="n">
-        <v>1690.265379310345</v>
+        <v>1437.764137931035</v>
       </c>
       <c r="FW3" t="n">
-        <v>1402.962206896552</v>
+        <v>1164.020689655172</v>
       </c>
       <c r="FX3" t="n">
-        <v>287.8624</v>
+        <v>244.963724137931</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.4157489933820969</v>
+        <v>0.5510221674876846</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.347018265412748</v>
+        <v>1.027847290640394</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.5958941135492861</v>
+        <v>0.1416489028213166</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.9923162661093698</v>
+        <v>1.145888042991491</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1193911202659121</v>
+        <v>0.112827644434879</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3863565764088865</v>
+        <v>0.4161756795551392</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.878624000000001</v>
+        <v>2.44963724137931</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.929835252586473</v>
+        <v>1.26889999156266</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.2161048403763808</v>
+        <v>0.1566811449389995</v>
       </c>
       <c r="GH3" t="n">
-        <v>1.814153704225135</v>
+        <v>1.614426364993379</v>
       </c>
       <c r="GI3" t="n">
-        <v>1.801181430254489</v>
+        <v>1.598438524011139</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.1515700498608281</v>
+        <v>0.1401264053007525</v>
       </c>
       <c r="GK3" t="n">
-        <v>-2.558620689655173</v>
+        <v>-0.3351724137931038</v>
       </c>
       <c r="GL3" t="n">
-        <v>-9.640275862068968</v>
+        <v>8.179310344827581</v>
       </c>
       <c r="GM3" t="n">
-        <v>-7.741793103448277</v>
+        <v>2.557241379310344</v>
       </c>
       <c r="GN3" t="n">
-        <v>-27.20579310344826</v>
+        <v>5.875862068965517</v>
       </c>
       <c r="GO3" t="n">
-        <v>-1.687172413793107</v>
+        <v>3.463448275862063</v>
       </c>
       <c r="GP3" t="n">
-        <v>2.915310344827589</v>
+        <v>1.438620689655172</v>
       </c>
       <c r="GQ3" t="n">
-        <v>1.927172413793109</v>
+        <v>-5.795862068965526</v>
       </c>
       <c r="GR3" t="n">
-        <v>-295.384</v>
+        <v>82.68413793103423</v>
       </c>
       <c r="GS3" t="n">
-        <v>-14.69158620689655</v>
+        <v>9.248275862068958</v>
       </c>
       <c r="GT3" t="n">
-        <v>-1.107310344827589</v>
+        <v>6.706206896551723</v>
       </c>
       <c r="GU3" t="n">
-        <v>-1.054068965517239</v>
+        <v>2.783448275862064</v>
       </c>
       <c r="GV3" t="n">
-        <v>29.78372413793103</v>
+        <v>-15.82896551724139</v>
       </c>
       <c r="GW3" t="n">
-        <v>-2.189241379310346</v>
+        <v>2.857931034482758</v>
       </c>
       <c r="GX3" t="n">
-        <v>-6.43586206896552</v>
+        <v>-1.168275862068967</v>
       </c>
       <c r="GY3" t="n">
-        <v>5.75200000000001</v>
+        <v>-13.16275862068967</v>
       </c>
       <c r="GZ3" t="n">
-        <v>46.12855172413791</v>
+        <v>-12.79034482758624</v>
       </c>
       <c r="HA3" t="n">
-        <v>-295.5384827586208</v>
+        <v>75.32827586206872</v>
       </c>
       <c r="HB3" t="n">
-        <v>-326.6863448275863</v>
+        <v>69.56275862068946</v>
       </c>
       <c r="HC3" t="n">
-        <v>-47.85288275862067</v>
+        <v>15.63158620689654</v>
       </c>
       <c r="HD3" t="n">
-        <v>-0.06980318057421508</v>
+        <v>-0.1369782803403493</v>
       </c>
       <c r="HE3" t="n">
-        <v>-0.4064074279743247</v>
+        <v>0.1213690103000444</v>
       </c>
       <c r="HF3" t="n">
-        <v>-0.3043333150011917</v>
+        <v>0.4444863412449619</v>
       </c>
       <c r="HG3" t="n">
-        <v>-0.163172890428789</v>
+        <v>-0.1936802507836991</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.02617629079108603</v>
+        <v>-0.006495841796322899</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.1462535826199058</v>
+        <v>-0.02344749493639997</v>
       </c>
       <c r="HJ3" t="n">
-        <v>-0.4785288275862074</v>
+        <v>0.1563158620689657</v>
       </c>
       <c r="HK3" t="n">
-        <v>-0.4480009799258982</v>
+        <v>0.2755539212985385</v>
       </c>
       <c r="HL3" t="n">
-        <v>-0.0448312527106553</v>
+        <v>0.03774295062268743</v>
       </c>
       <c r="HM3" t="n">
-        <v>-0.2809314199350423</v>
+        <v>0.05752703152351035</v>
       </c>
       <c r="HN3" t="n">
-        <v>-0.2531635051947414</v>
+        <v>0.063297472139908</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.04050602857615254</v>
+        <v>-0.001817628858273246</v>
       </c>
     </row>
     <row r="4">
@@ -2895,28 +2895,28 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -2952,10 +2952,10 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -2967,40 +2967,40 @@
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
@@ -3012,10 +3012,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>1</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
         <v>1</v>
@@ -3042,16 +3042,16 @@
         <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
         <v>1</v>
@@ -3060,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>1</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="n">
         <v>1</v>
@@ -3081,106 +3081,106 @@
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.282758620689655</v>
+        <v>2.517241379310345</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.241655172413792</v>
+        <v>2.786206896551724</v>
       </c>
       <c r="BO4" t="n">
-        <v>31.90179310344827</v>
+        <v>27.86206896551725</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.03144827586207</v>
+        <v>6.686896551724138</v>
       </c>
       <c r="BQ4" t="n">
-        <v>120.672</v>
+        <v>114.7917241379311</v>
       </c>
       <c r="BR4" t="n">
-        <v>42.30455172413792</v>
+        <v>25.63310344827586</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.774068965517241</v>
+        <v>8.358620689655172</v>
       </c>
       <c r="BT4" t="n">
-        <v>34.67586206896551</v>
+        <v>32.87724137931035</v>
       </c>
       <c r="BU4" t="n">
-        <v>1612.427586206896</v>
+        <v>1436.568275862069</v>
       </c>
       <c r="BV4" t="n">
-        <v>70.73875862068964</v>
+        <v>40.12137931034484</v>
       </c>
       <c r="BW4" t="n">
-        <v>31.20827586206896</v>
+        <v>27.3048275862069</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.99806896551723</v>
+        <v>45.13655172413793</v>
       </c>
       <c r="BY4" t="n">
-        <v>134.5423448275862</v>
+        <v>84.70068965517241</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.548137931034482</v>
+        <v>4.457931034482759</v>
       </c>
       <c r="CA4" t="n">
-        <v>36.75641379310344</v>
+        <v>37.33517241379311</v>
       </c>
       <c r="CB4" t="n">
-        <v>47.85268965517241</v>
+        <v>37.33517241379311</v>
       </c>
       <c r="CC4" t="n">
-        <v>196.9588965517241</v>
+        <v>176.6455172413793</v>
       </c>
       <c r="CD4" t="n">
-        <v>1185.914482758621</v>
+        <v>1107.795862068966</v>
       </c>
       <c r="CE4" t="n">
-        <v>890.4761379310344</v>
+        <v>840.3200000000002</v>
       </c>
       <c r="CF4" t="n">
-        <v>258.404524137931</v>
+        <v>195.7031724137931</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.7876374384236452</v>
+        <v>0.3728210180623974</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.943874787281684</v>
+        <v>0.6806305418719213</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.2421806239737274</v>
+        <v>0.2856576480990274</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.6854393543540549</v>
+        <v>0.7252472737989981</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1004166036791939</v>
+        <v>0.08301279602826647</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.5969927107839377</v>
+        <v>0.559238127332382</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.58404524137931</v>
+        <v>1.957031724137931</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.745865857590685</v>
+        <v>1.254145353113795</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1634019129972455</v>
+        <v>0.1253124779262635</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.219389645437542</v>
+        <v>1.144087758335079</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.343442852233819</v>
+        <v>1.214194240968232</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1091680059338047</v>
+        <v>0.1053469492784225</v>
       </c>
       <c r="CS4" t="n">
         <v>1</v>
       </c>
       <c r="CT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>1</v>
@@ -3189,25 +3189,25 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
         <v>0</v>
@@ -3237,16 +3237,16 @@
         <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
@@ -3258,49 +3258,49 @@
         <v>1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX4" t="n">
         <v>1</v>
       </c>
       <c r="DY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB4" t="n">
         <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG4" t="n">
         <v>1</v>
       </c>
       <c r="EH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>1</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>1</v>
@@ -3330,34 +3330,34 @@
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
         <v>1</v>
       </c>
       <c r="EV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
         <v>0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FB4" t="n">
         <v>1</v>
@@ -3369,198 +3369,198 @@
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>1.4</v>
+        <v>3.137931034482758</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.646344827586207</v>
+        <v>2.733241379310345</v>
       </c>
       <c r="FG4" t="n">
-        <v>26.13213793103448</v>
+        <v>31.43227586206896</v>
       </c>
       <c r="FH4" t="n">
-        <v>7.900413793103448</v>
+        <v>8.199724137931033</v>
       </c>
       <c r="FI4" t="n">
-        <v>130.6606896551724</v>
+        <v>183.1271724137931</v>
       </c>
       <c r="FJ4" t="n">
-        <v>30.38620689655172</v>
+        <v>36.21544827586207</v>
       </c>
       <c r="FK4" t="n">
-        <v>9.115862068965518</v>
+        <v>18.44937931034483</v>
       </c>
       <c r="FL4" t="n">
-        <v>48.01020689655173</v>
+        <v>89.51365517241379</v>
       </c>
       <c r="FM4" t="n">
-        <v>1678.534068965517</v>
+        <v>2096.396137931034</v>
       </c>
       <c r="FN4" t="n">
-        <v>55.91062068965517</v>
+        <v>47.14841379310345</v>
       </c>
       <c r="FO4" t="n">
-        <v>27.95531034482758</v>
+        <v>26.64910344827586</v>
       </c>
       <c r="FP4" t="n">
-        <v>43.14841379310344</v>
+        <v>43.73186206896552</v>
       </c>
       <c r="FQ4" t="n">
-        <v>99.05903448275862</v>
+        <v>69.0143448275862</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.646344827586207</v>
+        <v>6.149793103448276</v>
       </c>
       <c r="FS4" t="n">
-        <v>27.34758620689655</v>
+        <v>23.91586206896552</v>
       </c>
       <c r="FT4" t="n">
-        <v>45.57931034482758</v>
+        <v>68.33103448275862</v>
       </c>
       <c r="FU4" t="n">
-        <v>198.1180689655172</v>
+        <v>207.7263448275862</v>
       </c>
       <c r="FV4" t="n">
-        <v>1258.596689655172</v>
+        <v>1749.957793103448</v>
       </c>
       <c r="FW4" t="n">
-        <v>993.0212413793104</v>
+        <v>1417.185655172414</v>
       </c>
       <c r="FX4" t="n">
-        <v>236.7085517241379</v>
+        <v>276.4673655172414</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.3796302731751008</v>
+        <v>0.2622807384186694</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.9449101855998409</v>
+        <v>0.8462004876349704</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.417207443897099</v>
+        <v>0.5897002786485545</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.022519978106185</v>
+        <v>1.369640369209335</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.116080466006198</v>
+        <v>0.1729499023848577</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.5301422187383884</v>
+        <v>0.4133658709092037</v>
       </c>
       <c r="GE4" t="n">
-        <v>2.367085517241379</v>
+        <v>2.764673655172414</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.324413043562252</v>
+        <v>1.768926546612705</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1662527477375922</v>
+        <v>0.1698202968455523</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.313050757878575</v>
+        <v>1.839503544367052</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.363910483623451</v>
+        <v>1.807609797137307</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.1391102078665324</v>
+        <v>0.2086320809282718</v>
       </c>
       <c r="GK4" t="n">
-        <v>2.595310344827586</v>
+        <v>0.05296551724137943</v>
       </c>
       <c r="GL4" t="n">
-        <v>5.769655172413788</v>
+        <v>-3.570206896551717</v>
       </c>
       <c r="GM4" t="n">
-        <v>10.13103448275862</v>
+        <v>-1.512827586206895</v>
       </c>
       <c r="GN4" t="n">
-        <v>-9.988689655172436</v>
+        <v>-68.33544827586206</v>
       </c>
       <c r="GO4" t="n">
-        <v>11.9183448275862</v>
+        <v>-10.5823448275862</v>
       </c>
       <c r="GP4" t="n">
-        <v>-6.341793103448277</v>
+        <v>-10.09075862068966</v>
       </c>
       <c r="GQ4" t="n">
-        <v>-13.33434482758621</v>
+        <v>-56.63641379310344</v>
       </c>
       <c r="GR4" t="n">
-        <v>-66.10648275862081</v>
+        <v>-659.8278620689653</v>
       </c>
       <c r="GS4" t="n">
-        <v>14.82813793103447</v>
+        <v>-7.027034482758616</v>
       </c>
       <c r="GT4" t="n">
-        <v>3.252965517241378</v>
+        <v>0.6557241379310383</v>
       </c>
       <c r="GU4" t="n">
-        <v>-0.1503448275862098</v>
+        <v>1.404689655172412</v>
       </c>
       <c r="GV4" t="n">
-        <v>35.48331034482757</v>
+        <v>15.68634482758621</v>
       </c>
       <c r="GW4" t="n">
-        <v>1.901793103448275</v>
+        <v>-1.691862068965517</v>
       </c>
       <c r="GX4" t="n">
-        <v>9.40882758620689</v>
+        <v>13.41931034482759</v>
       </c>
       <c r="GY4" t="n">
-        <v>2.273379310344829</v>
+        <v>-30.99586206896551</v>
       </c>
       <c r="GZ4" t="n">
-        <v>-1.159172413793129</v>
+        <v>-31.08082758620688</v>
       </c>
       <c r="HA4" t="n">
-        <v>-72.68220689655186</v>
+        <v>-642.1619310344827</v>
       </c>
       <c r="HB4" t="n">
-        <v>-102.545103448276</v>
+        <v>-576.8656551724137</v>
       </c>
       <c r="HC4" t="n">
-        <v>21.6959724137931</v>
+        <v>-80.76419310344826</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.4080071652485444</v>
+        <v>0.1105402796437279</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.9989646016818429</v>
+        <v>-0.1655699457630491</v>
       </c>
       <c r="HF4" t="n">
-        <v>-0.1750268199233716</v>
+        <v>-0.304042630549527</v>
       </c>
       <c r="HG4" t="n">
-        <v>-0.33708062375213</v>
+        <v>-0.6443930954103367</v>
       </c>
       <c r="HH4" t="n">
-        <v>-0.01566386232700406</v>
+        <v>-0.08993710635659125</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.06685049204554927</v>
+        <v>0.1458722564231782</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.2169597241379306</v>
+        <v>-0.8076419310344825</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.4214528140284326</v>
+        <v>-0.5147811934989102</v>
       </c>
       <c r="HL4" t="n">
-        <v>-0.002850834740346697</v>
+        <v>-0.04450781891928882</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.09366111244103315</v>
+        <v>-0.6954157860319732</v>
       </c>
       <c r="HN4" t="n">
-        <v>-0.0204676313896317</v>
+        <v>-0.5934155561690746</v>
       </c>
       <c r="HO4" t="n">
-        <v>-0.02994220193272772</v>
+        <v>-0.1032851316498493</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -3581,13 +3581,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -3614,16 +3614,16 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -3632,25 +3632,25 @@
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -3668,34 +3668,34 @@
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI5" t="n">
         <v>1</v>
@@ -3746,115 +3746,115 @@
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.006896551724138</v>
+        <v>2.475862068965517</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.142344827586207</v>
+        <v>3.605241379310344</v>
       </c>
       <c r="BO5" t="n">
-        <v>28.47862068965517</v>
+        <v>26.78179310344827</v>
       </c>
       <c r="BP5" t="n">
-        <v>9.320275862068966</v>
+        <v>12.3608275862069</v>
       </c>
       <c r="BQ5" t="n">
-        <v>111.3255172413793</v>
+        <v>124.1233103448276</v>
       </c>
       <c r="BR5" t="n">
-        <v>20.71172413793104</v>
+        <v>20.60137931034483</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.731310344827587</v>
+        <v>11.84579310344827</v>
       </c>
       <c r="BT5" t="n">
-        <v>34.69213793103449</v>
+        <v>40.17268965517241</v>
       </c>
       <c r="BU5" t="n">
-        <v>1398.559172413793</v>
+        <v>1555.404137931034</v>
       </c>
       <c r="BV5" t="n">
-        <v>44.01241379310345</v>
+        <v>39.65765517241379</v>
       </c>
       <c r="BW5" t="n">
-        <v>26.40744827586207</v>
+        <v>15.96606896551724</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.95724137931035</v>
+        <v>39.65765517241379</v>
       </c>
       <c r="BY5" t="n">
-        <v>70.9376551724138</v>
+        <v>81.37544827586207</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.588965517241379</v>
+        <v>2.575172413793103</v>
       </c>
       <c r="CA5" t="n">
-        <v>25.8896551724138</v>
+        <v>19.05627586206896</v>
       </c>
       <c r="CB5" t="n">
-        <v>47.63696551724138</v>
+        <v>48.41324137931034</v>
       </c>
       <c r="CC5" t="n">
-        <v>189.512275862069</v>
+        <v>156.0554482758621</v>
       </c>
       <c r="CD5" t="n">
-        <v>1094.614620689655</v>
+        <v>1266.469793103448</v>
       </c>
       <c r="CE5" t="n">
-        <v>848.145103448276</v>
+        <v>1049.12524137931</v>
       </c>
       <c r="CF5" t="n">
-        <v>199.1950068965517</v>
+        <v>211.7821793103448</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3661278307898997</v>
+        <v>0.3378938349007314</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.8035362706259259</v>
+        <v>1.23151210628452</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1121885057471265</v>
+        <v>0.5162607553366173</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.7091734956051385</v>
+        <v>1.029511568890879</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.08185857451557337</v>
+        <v>0.08358080893419745</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.462915045925742</v>
+        <v>0.3311936868057165</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.991950068965517</v>
+        <v>2.117821793103448</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.535160432275803</v>
+        <v>1.316011857768338</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.126176729343575</v>
+        <v>0.1103455938986567</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.109912854839991</v>
+        <v>1.240059778270415</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.15230414964555</v>
+        <v>1.267445039027395</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.09802068985853096</v>
+        <v>0.1092958104708623</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
@@ -3866,19 +3866,19 @@
         <v>1</v>
       </c>
       <c r="CY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ5" t="n">
         <v>1</v>
       </c>
       <c r="DA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
         <v>1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK5" t="n">
         <v>1</v>
@@ -3908,10 +3908,10 @@
         <v>1</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
         <v>0</v>
@@ -3920,28 +3920,28 @@
         <v>1</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3950,16 +3950,16 @@
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE5" t="n">
         <v>1</v>
@@ -3974,16 +3974,16 @@
         <v>1</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3992,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP5" t="n">
         <v>1</v>
@@ -4004,229 +4004,229 @@
         <v>1</v>
       </c>
       <c r="ES5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV5" t="n">
         <v>1</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY5" t="n">
         <v>1</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB5" t="n">
         <v>0</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD5" t="n">
         <v>1</v>
       </c>
       <c r="FE5" t="n">
-        <v>3.468965517241379</v>
+        <v>3.282758620689655</v>
       </c>
       <c r="FF5" t="n">
-        <v>1.273931034482759</v>
+        <v>3.246896551724138</v>
       </c>
       <c r="FG5" t="n">
-        <v>36.30703448275863</v>
+        <v>29.87144827586207</v>
       </c>
       <c r="FH5" t="n">
-        <v>10.82841379310345</v>
+        <v>14.28634482758621</v>
       </c>
       <c r="FI5" t="n">
-        <v>175.8024827586207</v>
+        <v>129.2264827586207</v>
       </c>
       <c r="FJ5" t="n">
-        <v>28.0264827586207</v>
+        <v>37.01462068965517</v>
       </c>
       <c r="FK5" t="n">
-        <v>21.6568275862069</v>
+        <v>5.844413793103448</v>
       </c>
       <c r="FL5" t="n">
-        <v>67.51834482758622</v>
+        <v>42.85903448275862</v>
       </c>
       <c r="FM5" t="n">
-        <v>1898.794206896552</v>
+        <v>1635.137103448276</v>
       </c>
       <c r="FN5" t="n">
-        <v>38.85489655172415</v>
+        <v>58.44413793103448</v>
       </c>
       <c r="FO5" t="n">
-        <v>19.74593103448276</v>
+        <v>29.22206896551724</v>
       </c>
       <c r="FP5" t="n">
-        <v>32.48524137931035</v>
+        <v>42.20965517241379</v>
       </c>
       <c r="FQ5" t="n">
-        <v>50.95724137931035</v>
+        <v>122.7326896551724</v>
       </c>
       <c r="FR5" t="n">
-        <v>3.821793103448276</v>
+        <v>3.896275862068965</v>
       </c>
       <c r="FS5" t="n">
-        <v>28.66344827586207</v>
+        <v>36.36524137931034</v>
       </c>
       <c r="FT5" t="n">
-        <v>51.59420689655173</v>
+        <v>48.05406896551725</v>
       </c>
       <c r="FU5" t="n">
-        <v>199.3702068965518</v>
+        <v>200.6582068965517</v>
       </c>
       <c r="FV5" t="n">
-        <v>1605.790068965518</v>
+        <v>1261.094620689655</v>
       </c>
       <c r="FW5" t="n">
-        <v>1306.416275862069</v>
+        <v>971.471448275862</v>
       </c>
       <c r="FX5" t="n">
-        <v>252.3657379310345</v>
+        <v>246.829075862069</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.07077394636015326</v>
+        <v>0.5519724137931034</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.261761758638027</v>
+        <v>1.634622660098522</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.5039104980842912</v>
+        <v>0.1185374931581828</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.084787662835249</v>
+        <v>0.4794707015106289</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.1270872973811641</v>
+        <v>0.1096604689721382</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.4494891636054933</v>
+        <v>0.5426842907942674</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.523657379310345</v>
+        <v>2.468290758620689</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.397785440613027</v>
+        <v>1.561993089925625</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.1696207026750504</v>
+        <v>0.150067583401166</v>
       </c>
       <c r="GH5" t="n">
-        <v>1.757047520671741</v>
+        <v>1.299152339917866</v>
       </c>
       <c r="GI5" t="n">
-        <v>1.676069221643139</v>
+        <v>1.374536177152107</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.1675173823761291</v>
+        <v>0.1238788273305248</v>
       </c>
       <c r="GK5" t="n">
-        <v>2.868413793103448</v>
+        <v>0.358344827586206</v>
       </c>
       <c r="GL5" t="n">
-        <v>-7.828413793103458</v>
+        <v>-3.089655172413796</v>
       </c>
       <c r="GM5" t="n">
-        <v>-1.508137931034483</v>
+        <v>-1.925517241379312</v>
       </c>
       <c r="GN5" t="n">
-        <v>-64.47696551724141</v>
+        <v>-5.103172413793104</v>
       </c>
       <c r="GO5" t="n">
-        <v>-7.314758620689663</v>
+        <v>-16.41324137931035</v>
       </c>
       <c r="GP5" t="n">
-        <v>-14.92551724137931</v>
+        <v>6.001379310344825</v>
       </c>
       <c r="GQ5" t="n">
-        <v>-32.82620689655173</v>
+        <v>-2.686344827586211</v>
       </c>
       <c r="GR5" t="n">
-        <v>-500.2350344827589</v>
+        <v>-79.73296551724161</v>
       </c>
       <c r="GS5" t="n">
-        <v>5.157517241379303</v>
+        <v>-18.78648275862069</v>
       </c>
       <c r="GT5" t="n">
-        <v>6.661517241379308</v>
+        <v>-13.256</v>
       </c>
       <c r="GU5" t="n">
-        <v>24.472</v>
+        <v>-2.552</v>
       </c>
       <c r="GV5" t="n">
-        <v>19.98041379310344</v>
+        <v>-41.35724137931034</v>
       </c>
       <c r="GW5" t="n">
-        <v>-1.232827586206897</v>
+        <v>-1.321103448275862</v>
       </c>
       <c r="GX5" t="n">
-        <v>-2.773793103448277</v>
+        <v>-17.30896551724138</v>
       </c>
       <c r="GY5" t="n">
-        <v>-3.957241379310354</v>
+        <v>0.3591724137930967</v>
       </c>
       <c r="GZ5" t="n">
-        <v>-9.857931034482789</v>
+        <v>-44.60275862068966</v>
       </c>
       <c r="HA5" t="n">
-        <v>-511.1754482758622</v>
+        <v>5.375172413793052</v>
       </c>
       <c r="HB5" t="n">
-        <v>-458.2711724137931</v>
+        <v>77.65379310344815</v>
       </c>
       <c r="HC5" t="n">
-        <v>-53.1707310344828</v>
+        <v>-35.04689655172419</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.2953538844297465</v>
+        <v>-0.214078578892372</v>
       </c>
       <c r="HE5" t="n">
-        <v>-0.4582254880121008</v>
+        <v>-0.4031105538140023</v>
       </c>
       <c r="HF5" t="n">
-        <v>-0.3917219923371648</v>
+        <v>0.3977232621784345</v>
       </c>
       <c r="HG5" t="n">
-        <v>-0.3756141672301108</v>
+        <v>0.5500408673802502</v>
       </c>
       <c r="HH5" t="n">
-        <v>-0.04522872286559075</v>
+        <v>-0.02607966003794079</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.01342588232024866</v>
+        <v>-0.2114906039885509</v>
       </c>
       <c r="HJ5" t="n">
-        <v>-0.5317073103448284</v>
+        <v>-0.3504689655172415</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.1373749916627758</v>
+        <v>-0.2459812321572874</v>
       </c>
       <c r="HL5" t="n">
-        <v>-0.04344397333147543</v>
+        <v>-0.03972198950250937</v>
       </c>
       <c r="HM5" t="n">
-        <v>-0.6471346658317494</v>
+        <v>-0.05909256164745136</v>
       </c>
       <c r="HN5" t="n">
-        <v>-0.5237650719975897</v>
+        <v>-0.1070911381247117</v>
       </c>
       <c r="HO5" t="n">
-        <v>-0.06949669251759819</v>
+        <v>-0.0145830168596625</v>
       </c>
     </row>
     <row r="6">
@@ -4234,19 +4234,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -4258,19 +4258,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -4279,13 +4279,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -4294,13 +4294,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -4309,43 +4309,43 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -4354,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -4369,19 +4369,19 @@
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
         <v>1</v>
@@ -4390,25 +4390,25 @@
         <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE6" t="n">
         <v>1</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG6" t="n">
         <v>1</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI6" t="n">
         <v>0</v>
@@ -4417,106 +4417,106 @@
         <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.917241379310345</v>
+        <v>2.503448275862069</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.417931034482758</v>
+        <v>2.009379310344828</v>
       </c>
       <c r="BO6" t="n">
-        <v>41.0151724137931</v>
+        <v>35.49903448275862</v>
       </c>
       <c r="BP6" t="n">
-        <v>10.93737931034483</v>
+        <v>11.38648275862069</v>
       </c>
       <c r="BQ6" t="n">
-        <v>168.1622068965517</v>
+        <v>156.0617931034483</v>
       </c>
       <c r="BR6" t="n">
-        <v>43.06593103448275</v>
+        <v>45.54593103448276</v>
       </c>
       <c r="BS6" t="n">
-        <v>13.67172413793103</v>
+        <v>14.06565517241379</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.88993103448275</v>
+        <v>58.94179310344828</v>
       </c>
       <c r="BU6" t="n">
-        <v>1937.966896551724</v>
+        <v>1874.750896551724</v>
       </c>
       <c r="BV6" t="n">
-        <v>62.2063448275862</v>
+        <v>73.67724137931035</v>
       </c>
       <c r="BW6" t="n">
-        <v>22.5583448275862</v>
+        <v>29.47089655172414</v>
       </c>
       <c r="BX6" t="n">
-        <v>49.21820689655172</v>
+        <v>49.56468965517242</v>
       </c>
       <c r="BY6" t="n">
-        <v>85.44827586206895</v>
+        <v>89.0824827586207</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.785103448275861</v>
+        <v>7.367724137931035</v>
       </c>
       <c r="CA6" t="n">
-        <v>30.07779310344828</v>
+        <v>22.1031724137931</v>
       </c>
       <c r="CB6" t="n">
-        <v>59.47199999999999</v>
+        <v>75.68662068965517</v>
       </c>
       <c r="CC6" t="n">
-        <v>223.5326896551724</v>
+        <v>231.7484137931035</v>
       </c>
       <c r="CD6" t="n">
-        <v>1559.260137931034</v>
+        <v>1490.289655172414</v>
       </c>
       <c r="CE6" t="n">
-        <v>1270.103172413793</v>
+        <v>1155.393103448276</v>
       </c>
       <c r="CF6" t="n">
-        <v>278.4246620689655</v>
+        <v>257.9373241379311</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.2784111405835544</v>
+        <v>0.1488429118773946</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.8720248372317336</v>
+        <v>1.032597701149425</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.4745127646702963</v>
+        <v>0.5207764052039913</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.157899092558984</v>
+        <v>1.166004294556019</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1379295253983313</v>
+        <v>0.1359395637544964</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.4900188339946072</v>
+        <v>0.5382965836423322</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.784246620689655</v>
+        <v>2.57937324137931</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.623271210906175</v>
+        <v>1.623591615956727</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1769314128243849</v>
+        <v>0.2093404054653763</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.678246293612459</v>
+        <v>1.568615417008622</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.680428718394844</v>
+        <v>1.57910141027219</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1676914642813709</v>
+        <v>0.1683969200495517</v>
       </c>
       <c r="CS6" t="n">
         <v>1</v>
@@ -4714,204 +4714,204 @@
         <v>2.531034482758621</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.069793103448275</v>
+        <v>1.368827586206897</v>
       </c>
       <c r="FG6" t="n">
-        <v>44.15558620689655</v>
+        <v>42.4336551724138</v>
       </c>
       <c r="FH6" t="n">
-        <v>6.209379310344827</v>
+        <v>6.159724137931035</v>
       </c>
       <c r="FI6" t="n">
-        <v>153.8546206896552</v>
+        <v>156.0463448275862</v>
       </c>
       <c r="FJ6" t="n">
-        <v>31.73682758620689</v>
+        <v>34.22068965517241</v>
       </c>
       <c r="FK6" t="n">
-        <v>21.38786206896552</v>
+        <v>19.848</v>
       </c>
       <c r="FL6" t="n">
-        <v>83.48165517241378</v>
+        <v>71.86344827586207</v>
       </c>
       <c r="FM6" t="n">
-        <v>1911.108965517241</v>
+        <v>1908.145655172414</v>
       </c>
       <c r="FN6" t="n">
-        <v>66.23337931034482</v>
+        <v>62.28165517241379</v>
       </c>
       <c r="FO6" t="n">
-        <v>29.66703448275862</v>
+        <v>30.11420689655173</v>
       </c>
       <c r="FP6" t="n">
-        <v>48.2951724137931</v>
+        <v>52.01544827586207</v>
       </c>
       <c r="FQ6" t="n">
-        <v>66.92331034482758</v>
+        <v>73.23227586206896</v>
       </c>
       <c r="FR6" t="n">
-        <v>2.759724137931034</v>
+        <v>4.10648275862069</v>
       </c>
       <c r="FS6" t="n">
-        <v>21.38786206896552</v>
+        <v>23.27006896551724</v>
       </c>
       <c r="FT6" t="n">
-        <v>64.16358620689655</v>
+        <v>62.28165517241379</v>
       </c>
       <c r="FU6" t="n">
-        <v>244.2355862068965</v>
+        <v>225.8565517241379</v>
       </c>
       <c r="FV6" t="n">
-        <v>1529.577103448276</v>
+        <v>1533.771310344828</v>
       </c>
       <c r="FW6" t="n">
-        <v>1149.425103448276</v>
+        <v>1179.244965517242</v>
       </c>
       <c r="FX6" t="n">
-        <v>258.1721931034483</v>
+        <v>262.6095724137932</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.12830296430732</v>
+        <v>0.07024246823956443</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.6130702964307319</v>
+        <v>0.6423883847549909</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.5627413841629706</v>
+        <v>0.5870586760095888</v>
       </c>
       <c r="GB6" t="n">
-        <v>1.199237508301456</v>
+        <v>1.276099712863202</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1791426592629948</v>
+        <v>0.1492228236135234</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.5554152713483942</v>
+        <v>0.5042622805934767</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.581721931034483</v>
+        <v>2.626095724137932</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.308776670675826</v>
+        <v>1.50475067370621</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.1781245254978835</v>
+        <v>0.1760707987320616</v>
       </c>
       <c r="GH6" t="n">
-        <v>1.53970576896608</v>
+        <v>1.558998777401857</v>
       </c>
       <c r="GI6" t="n">
-        <v>1.554084273742468</v>
+        <v>1.566490716548816</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.2248506062590645</v>
+        <v>0.1908724593180044</v>
       </c>
       <c r="GK6" t="n">
-        <v>1.348137931034483</v>
+        <v>0.6405517241379308</v>
       </c>
       <c r="GL6" t="n">
-        <v>-3.140413793103455</v>
+        <v>-6.934620689655183</v>
       </c>
       <c r="GM6" t="n">
-        <v>4.728</v>
+        <v>5.226758620689654</v>
       </c>
       <c r="GN6" t="n">
-        <v>14.30758620689653</v>
+        <v>0.0154482758620702</v>
       </c>
       <c r="GO6" t="n">
-        <v>11.32910344827586</v>
+        <v>11.32524137931034</v>
       </c>
       <c r="GP6" t="n">
-        <v>-7.716137931034485</v>
+        <v>-5.782344827586206</v>
       </c>
       <c r="GQ6" t="n">
-        <v>-20.59172413793103</v>
+        <v>-12.92165517241379</v>
       </c>
       <c r="GR6" t="n">
-        <v>26.85793103448259</v>
+        <v>-33.39475862069003</v>
       </c>
       <c r="GS6" t="n">
-        <v>-4.027034482758616</v>
+        <v>11.39558620689655</v>
       </c>
       <c r="GT6" t="n">
-        <v>-7.108689655172412</v>
+        <v>-0.6433103448275901</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.9230344827586165</v>
+        <v>-2.450758620689655</v>
       </c>
       <c r="GV6" t="n">
-        <v>18.52496551724137</v>
+        <v>15.85020689655174</v>
       </c>
       <c r="GW6" t="n">
-        <v>2.025379310344827</v>
+        <v>3.261241379310345</v>
       </c>
       <c r="GX6" t="n">
-        <v>8.689931034482758</v>
+        <v>-1.16689655172414</v>
       </c>
       <c r="GY6" t="n">
-        <v>-4.691586206896567</v>
+        <v>13.40496551724138</v>
       </c>
       <c r="GZ6" t="n">
-        <v>-20.70289655172411</v>
+        <v>5.891862068965509</v>
       </c>
       <c r="HA6" t="n">
-        <v>29.68303448275856</v>
+        <v>-43.48165517241387</v>
       </c>
       <c r="HB6" t="n">
-        <v>120.6780689655172</v>
+        <v>-23.8518620689656</v>
       </c>
       <c r="HC6" t="n">
-        <v>20.25246896551721</v>
+        <v>-4.672248275862103</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.1501081762762344</v>
+        <v>0.0786004436378302</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.2589545408010018</v>
+        <v>0.3902093163944342</v>
       </c>
       <c r="HF6" t="n">
-        <v>-0.08822861949267424</v>
+        <v>-0.06628227080559757</v>
       </c>
       <c r="HG6" t="n">
-        <v>-0.04133841574247255</v>
+        <v>-0.1100954183071829</v>
       </c>
       <c r="HH6" t="n">
-        <v>-0.04121313386466346</v>
+        <v>-0.01328325985902701</v>
       </c>
       <c r="HI6" t="n">
-        <v>-0.06539643735378697</v>
+        <v>0.03403430304885557</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.2025246896551725</v>
+        <v>-0.04672248275862145</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3144945402303485</v>
+        <v>0.1188409422505179</v>
       </c>
       <c r="HL6" t="n">
-        <v>-0.001193112673498614</v>
+        <v>0.03326960673331469</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.1385405246463784</v>
+        <v>0.009616639606765842</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1263444446523754</v>
+        <v>0.01261069372337453</v>
       </c>
       <c r="HO6" t="n">
-        <v>-0.05715914197769356</v>
+        <v>-0.02247553926845269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4953,40 +4953,40 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -5004,52 +5004,52 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
         <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
         <v>1</v>
@@ -5061,16 +5061,16 @@
         <v>1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>1</v>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ7" t="n">
         <v>0</v>
@@ -5094,100 +5094,100 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.475862068965517</v>
+        <v>3.006896551724138</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.429517241379311</v>
+        <v>4.174344827586206</v>
       </c>
       <c r="BO7" t="n">
-        <v>46.45931034482759</v>
+        <v>64.70234482758622</v>
       </c>
       <c r="BP7" t="n">
-        <v>13.58041379310345</v>
+        <v>18.0888275862069</v>
       </c>
       <c r="BQ7" t="n">
-        <v>191.5553103448276</v>
+        <v>202.455724137931</v>
       </c>
       <c r="BR7" t="n">
-        <v>45.74455172413794</v>
+        <v>32.69903448275862</v>
       </c>
       <c r="BS7" t="n">
-        <v>26.44606896551725</v>
+        <v>16.69737931034483</v>
       </c>
       <c r="BT7" t="n">
-        <v>95.06289655172415</v>
+        <v>67.48524137931034</v>
       </c>
       <c r="BU7" t="n">
-        <v>2084.950896551724</v>
+        <v>2268.756413793104</v>
       </c>
       <c r="BV7" t="n">
-        <v>45.02979310344828</v>
+        <v>68.18096551724139</v>
       </c>
       <c r="BW7" t="n">
-        <v>27.87558620689655</v>
+        <v>22.2631724137931</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.61020689655173</v>
+        <v>67.48524137931034</v>
       </c>
       <c r="BY7" t="n">
-        <v>72.19062068965518</v>
+        <v>70.96386206896551</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7147586206896553</v>
+        <v>7.65296551724138</v>
       </c>
       <c r="CA7" t="n">
-        <v>22.15751724137931</v>
+        <v>20.87172413793103</v>
       </c>
       <c r="CB7" t="n">
-        <v>70.04634482758622</v>
+        <v>63.31089655172413</v>
       </c>
       <c r="CC7" t="n">
-        <v>235.1555862068966</v>
+        <v>239.3291034482758</v>
       </c>
       <c r="CD7" t="n">
-        <v>1727.571586206897</v>
+        <v>1877.759448275862</v>
       </c>
       <c r="CE7" t="n">
-        <v>1383.057931034483</v>
+        <v>1538.941793103448</v>
       </c>
       <c r="CF7" t="n">
-        <v>280.8286620689656</v>
+        <v>284.4120275862069</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.1429517241379311</v>
+        <v>0.2164475095785441</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.034673167197914</v>
+        <v>0.9588343573667711</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.539472577996716</v>
+        <v>0.52327969348659</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.902619376026273</v>
+        <v>1.177379310344828</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.2084819847520119</v>
+        <v>0.1248349734095316</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.5205820684337527</v>
+        <v>0.4541092166829875</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.808286620689656</v>
+        <v>2.844120275862069</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.054218555793874</v>
+        <v>1.834218449182252</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1814230586560451</v>
+        <v>0.2372397561340888</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.918850757709117</v>
+        <v>2.024508392093271</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.884620608155469</v>
+        <v>1.960009416126539</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.2660474151202596</v>
+        <v>0.1566449413713848</v>
       </c>
       <c r="CS7" t="n">
         <v>1</v>
@@ -5217,28 +5217,28 @@
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
         <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
@@ -5253,13 +5253,13 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -5274,16 +5274,16 @@
         <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -5295,49 +5295,49 @@
         <v>1</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
         <v>1</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ7" t="n">
         <v>1</v>
@@ -5355,16 +5355,16 @@
         <v>1</v>
       </c>
       <c r="EV7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>1</v>
       </c>
       <c r="EY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ7" t="n">
         <v>1</v>
@@ -5376,199 +5376,199 @@
         <v>1</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>2.503448275862069</v>
+        <v>3.793103448275862</v>
       </c>
       <c r="FF7" t="n">
-        <v>3.310344827586207</v>
+        <v>5.966896551724139</v>
       </c>
       <c r="FG7" t="n">
-        <v>37.73793103448276</v>
+        <v>38.7848275862069</v>
       </c>
       <c r="FH7" t="n">
-        <v>11.2551724137931</v>
+        <v>13.12717241379311</v>
       </c>
       <c r="FI7" t="n">
-        <v>171.4758620689655</v>
+        <v>177.2168275862069</v>
       </c>
       <c r="FJ7" t="n">
-        <v>39.06206896551725</v>
+        <v>30.4311724137931</v>
       </c>
       <c r="FK7" t="n">
-        <v>17.21379310344828</v>
+        <v>19.09406896551724</v>
       </c>
       <c r="FL7" t="n">
-        <v>60.24827586206897</v>
+        <v>50.71862068965518</v>
       </c>
       <c r="FM7" t="n">
-        <v>2026.593103448276</v>
+        <v>2000.700413793104</v>
       </c>
       <c r="FN7" t="n">
-        <v>74.15172413793104</v>
+        <v>48.33186206896552</v>
       </c>
       <c r="FO7" t="n">
-        <v>21.18620689655173</v>
+        <v>29.83448275862069</v>
       </c>
       <c r="FP7" t="n">
-        <v>47.00689655172414</v>
+        <v>42.9616551724138</v>
       </c>
       <c r="FQ7" t="n">
-        <v>73.4896551724138</v>
+        <v>76.37627586206898</v>
       </c>
       <c r="FR7" t="n">
-        <v>7.282758620689656</v>
+        <v>5.966896551724139</v>
       </c>
       <c r="FS7" t="n">
-        <v>19.2</v>
+        <v>19.09406896551724</v>
       </c>
       <c r="FT7" t="n">
-        <v>82.75862068965519</v>
+        <v>53.70206896551725</v>
       </c>
       <c r="FU7" t="n">
-        <v>210.5379310344828</v>
+        <v>162.896275862069</v>
       </c>
       <c r="FV7" t="n">
-        <v>1663.11724137931</v>
+        <v>1685.051586206897</v>
       </c>
       <c r="FW7" t="n">
-        <v>1334.731034482759</v>
+        <v>1435.635310344828</v>
       </c>
       <c r="FX7" t="n">
-        <v>262.576551724138</v>
+        <v>252.9964137931035</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2574712643678161</v>
+        <v>0.5221034482758621</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.9379310344827587</v>
+        <v>1.082154264972777</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.6625539977264117</v>
+        <v>0.2202068965517241</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.459946949602122</v>
+        <v>0.9304225705329155</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.1262702420625572</v>
+        <v>0.08837540489277197</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.4447282756942415</v>
+        <v>0.2941424242511276</v>
       </c>
       <c r="GE7" t="n">
-        <v>2.625765517241379</v>
+        <v>2.529964137931034</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.666995073891626</v>
+        <v>1.634577869817772</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.2110360479029409</v>
+        <v>0.2098569987279798</v>
       </c>
       <c r="GH7" t="n">
-        <v>1.720070469322147</v>
+        <v>1.764706637375636</v>
       </c>
       <c r="GI7" t="n">
-        <v>1.679854577667995</v>
+        <v>1.703048300816552</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.1603369540084437</v>
+        <v>0.1217612627506066</v>
       </c>
       <c r="GK7" t="n">
-        <v>-1.880827586206897</v>
+        <v>-1.792551724137932</v>
       </c>
       <c r="GL7" t="n">
-        <v>8.72137931034483</v>
+        <v>25.91751724137931</v>
       </c>
       <c r="GM7" t="n">
-        <v>2.325241379310345</v>
+        <v>4.96165517241379</v>
       </c>
       <c r="GN7" t="n">
-        <v>20.07944827586209</v>
+        <v>25.23889655172414</v>
       </c>
       <c r="GO7" t="n">
-        <v>6.682482758620694</v>
+        <v>2.267862068965517</v>
       </c>
       <c r="GP7" t="n">
-        <v>9.232275862068967</v>
+        <v>-2.39668965517242</v>
       </c>
       <c r="GQ7" t="n">
-        <v>34.81462068965518</v>
+        <v>16.76662068965516</v>
       </c>
       <c r="GR7" t="n">
-        <v>58.3577931034481</v>
+        <v>268.0559999999998</v>
       </c>
       <c r="GS7" t="n">
-        <v>-29.12193103448276</v>
+        <v>19.84910344827587</v>
       </c>
       <c r="GT7" t="n">
-        <v>6.689379310344826</v>
+        <v>-7.571310344827591</v>
       </c>
       <c r="GU7" t="n">
-        <v>11.60331034482759</v>
+        <v>24.52358620689654</v>
       </c>
       <c r="GV7" t="n">
-        <v>-1.299034482758628</v>
+        <v>-5.412413793103468</v>
       </c>
       <c r="GW7" t="n">
-        <v>-6.568000000000001</v>
+        <v>1.686068965517241</v>
       </c>
       <c r="GX7" t="n">
-        <v>2.95751724137931</v>
+        <v>1.777655172413787</v>
       </c>
       <c r="GY7" t="n">
-        <v>-12.71227586206896</v>
+        <v>9.608827586206885</v>
       </c>
       <c r="GZ7" t="n">
-        <v>24.61765517241378</v>
+        <v>76.43282758620686</v>
       </c>
       <c r="HA7" t="n">
-        <v>64.45434482758628</v>
+        <v>192.7078620689651</v>
       </c>
       <c r="HB7" t="n">
-        <v>48.32689655172408</v>
+        <v>103.3064827586204</v>
       </c>
       <c r="HC7" t="n">
-        <v>18.25211034482766</v>
+        <v>31.4156137931034</v>
       </c>
       <c r="HD7" t="n">
-        <v>-0.114519540229885</v>
+        <v>-0.305655938697318</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.09674213271515519</v>
+        <v>-0.1233199076060058</v>
       </c>
       <c r="HF7" t="n">
-        <v>-0.1230814197296957</v>
+        <v>0.3030727969348659</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.4426724264241508</v>
+        <v>0.246956739811912</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.08221174268945475</v>
+        <v>0.03645956851675961</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.07585379273951115</v>
+        <v>0.1599667924318599</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.1825211034482761</v>
+        <v>0.3141561379310347</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.387223481902248</v>
+        <v>0.19964057936448</v>
       </c>
       <c r="HL7" t="n">
-        <v>-0.02961298924689582</v>
+        <v>0.02738275740610902</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.19878028838697</v>
+        <v>0.259801754717635</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.2047660304874748</v>
+        <v>0.2569611153099873</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.1057104611118158</v>
+        <v>0.03488367862077818</v>
       </c>
     </row>
     <row r="8">
@@ -5576,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -5585,10 +5585,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -5597,43 +5597,43 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -5642,16 +5642,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
@@ -5666,10 +5666,10 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -5678,10 +5678,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>1</v>
@@ -5690,10 +5690,10 @@
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -5714,10 +5714,10 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC8" t="n">
         <v>1</v>
@@ -5741,124 +5741,124 @@
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.475862068965517</v>
+        <v>2.917241379310345</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.146758620689655</v>
+        <v>1.982068965517241</v>
       </c>
       <c r="BO8" t="n">
-        <v>31.61903448275861</v>
+        <v>32.37379310344828</v>
       </c>
       <c r="BP8" t="n">
-        <v>12.95862068965517</v>
+        <v>7.928275862068966</v>
       </c>
       <c r="BQ8" t="n">
-        <v>137.3613793103448</v>
+        <v>165.8331034482759</v>
       </c>
       <c r="BR8" t="n">
-        <v>23.84386206896551</v>
+        <v>49.55172413793104</v>
       </c>
       <c r="BS8" t="n">
-        <v>15.032</v>
+        <v>13.21379310344828</v>
       </c>
       <c r="BT8" t="n">
-        <v>50.27944827586205</v>
+        <v>63.42620689655173</v>
       </c>
       <c r="BU8" t="n">
-        <v>1689.804137931034</v>
+        <v>1935.16</v>
       </c>
       <c r="BV8" t="n">
-        <v>43.02262068965516</v>
+        <v>63.42620689655173</v>
       </c>
       <c r="BW8" t="n">
-        <v>17.10537931034482</v>
+        <v>21.80275862068966</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.35751724137931</v>
+        <v>43.60551724137931</v>
       </c>
       <c r="BY8" t="n">
-        <v>77.23337931034482</v>
+        <v>73.33655172413793</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.591724137931034</v>
+        <v>5.285517241379311</v>
       </c>
       <c r="CA8" t="n">
-        <v>16.58703448275862</v>
+        <v>25.76689655172414</v>
       </c>
       <c r="CB8" t="n">
-        <v>48.72441379310344</v>
+        <v>67.3903448275862</v>
       </c>
       <c r="CC8" t="n">
-        <v>153.4300689655172</v>
+        <v>216.0455172413793</v>
       </c>
       <c r="CD8" t="n">
-        <v>1385.535724137931</v>
+        <v>1575.744827586207</v>
       </c>
       <c r="CE8" t="n">
-        <v>1161.092413793103</v>
+        <v>1280.416551724138</v>
       </c>
       <c r="CF8" t="n">
-        <v>216.6681379310344</v>
+        <v>268.4382068965518</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.3724621734587251</v>
+        <v>0.2773444486547935</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.105213270637408</v>
+        <v>0.9501786489372698</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.5121740558292281</v>
+        <v>0.3264811453922161</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.110177937005523</v>
+        <v>1.053046581972172</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.09659505923354554</v>
+        <v>0.1324182032210965</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.2879053191503867</v>
+        <v>0.4548600157027189</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.166681379310344</v>
+        <v>2.684382068965518</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.316348891677878</v>
+        <v>1.480414919616604</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1316998643941555</v>
+        <v>0.1778276720496728</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.36998766339885</v>
+        <v>1.65621753707424</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.364757137250055</v>
+        <v>1.642355533914228</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.1269113786228383</v>
+        <v>0.1601607773927243</v>
       </c>
       <c r="CS8" t="n">
         <v>1</v>
@@ -5867,25 +5867,25 @@
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW8" t="n">
         <v>1</v>
       </c>
       <c r="CX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>1</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
         <v>1</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -5909,55 +5909,55 @@
         <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>1</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR8" t="n">
         <v>1</v>
       </c>
       <c r="DS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>1</v>
       </c>
       <c r="DU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
@@ -5966,19 +5966,19 @@
         <v>0</v>
       </c>
       <c r="EB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG8" t="n">
         <v>1</v>
@@ -5990,19 +5990,19 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
         <v>1</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET8" t="n">
         <v>1</v>
       </c>
       <c r="EU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -6032,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ8" t="n">
         <v>1</v>
@@ -6050,216 +6050,216 @@
         <v>1</v>
       </c>
       <c r="FD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>3.055172413793104</v>
+        <v>3.103448275862069</v>
       </c>
       <c r="FF8" t="n">
-        <v>3.904551724137931</v>
+        <v>3.432827586206896</v>
       </c>
       <c r="FG8" t="n">
-        <v>25.37958620689655</v>
+        <v>25.17406896551724</v>
       </c>
       <c r="FH8" t="n">
-        <v>9.110620689655173</v>
+        <v>10.29848275862069</v>
       </c>
       <c r="FI8" t="n">
-        <v>151.6267586206897</v>
+        <v>114.999724137931</v>
       </c>
       <c r="FJ8" t="n">
-        <v>44.25158620689655</v>
+        <v>34.32827586206896</v>
       </c>
       <c r="FK8" t="n">
-        <v>7.158344827586208</v>
+        <v>10.87062068965517</v>
       </c>
       <c r="FL8" t="n">
-        <v>46.85462068965518</v>
+        <v>42.33820689655172</v>
       </c>
       <c r="FM8" t="n">
-        <v>1734.271724137931</v>
+        <v>1402.310068965517</v>
       </c>
       <c r="FN8" t="n">
-        <v>48.15613793103449</v>
+        <v>55.49737931034482</v>
       </c>
       <c r="FO8" t="n">
-        <v>23.42731034482759</v>
+        <v>18.30841379310345</v>
       </c>
       <c r="FP8" t="n">
-        <v>34.49020689655173</v>
+        <v>42.9103448275862</v>
       </c>
       <c r="FQ8" t="n">
-        <v>109.9782068965517</v>
+        <v>94.97489655172413</v>
       </c>
       <c r="FR8" t="n">
-        <v>2.603034482758621</v>
+        <v>2.860689655172413</v>
       </c>
       <c r="FS8" t="n">
-        <v>29.28413793103449</v>
+        <v>23.45765517241379</v>
       </c>
       <c r="FT8" t="n">
-        <v>63.77434482758622</v>
+        <v>46.91531034482757</v>
       </c>
       <c r="FU8" t="n">
-        <v>188.72</v>
+        <v>181.9398620689655</v>
       </c>
       <c r="FV8" t="n">
-        <v>1342.515034482759</v>
+        <v>1030.992551724138</v>
       </c>
       <c r="FW8" t="n">
-        <v>1075.704</v>
+        <v>785.5453793103449</v>
       </c>
       <c r="FX8" t="n">
-        <v>258.3511724137932</v>
+        <v>214.3228689655172</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.4473965517241379</v>
+        <v>0.4299766746663298</v>
       </c>
       <c r="FZ8" t="n">
-        <v>1.079174712643678</v>
+        <v>1.175362721569618</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.2231641936607454</v>
+        <v>0.3633653779171021</v>
       </c>
       <c r="GB8" t="n">
-        <v>1.10159442702891</v>
+        <v>0.836662486938349</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1054603571763424</v>
+        <v>0.124429556782916</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.479969760255558</v>
+        <v>0.5426952668900878</v>
       </c>
       <c r="GE8" t="n">
-        <v>2.583511724137931</v>
+        <v>2.143228689655172</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.369985916132843</v>
+        <v>1.2504320097527</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.1533713761195991</v>
+        <v>0.1381740992537057</v>
       </c>
       <c r="GH8" t="n">
-        <v>1.518454777666308</v>
+        <v>1.151465752264984</v>
       </c>
       <c r="GI8" t="n">
-        <v>1.55676922930416</v>
+        <v>1.236082477300586</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.1224492248547628</v>
+        <v>0.1554943157626798</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.2422068965517234</v>
+        <v>-1.450758620689655</v>
       </c>
       <c r="GL8" t="n">
-        <v>6.239448275862056</v>
+        <v>7.199724137931039</v>
       </c>
       <c r="GM8" t="n">
-        <v>3.847999999999997</v>
+        <v>-2.370206896551722</v>
       </c>
       <c r="GN8" t="n">
-        <v>-14.26537931034488</v>
+        <v>50.83337931034487</v>
       </c>
       <c r="GO8" t="n">
-        <v>-20.40772413793104</v>
+        <v>15.22344827586208</v>
       </c>
       <c r="GP8" t="n">
-        <v>7.873655172413788</v>
+        <v>2.343172413793106</v>
       </c>
       <c r="GQ8" t="n">
-        <v>3.424827586206874</v>
+        <v>21.088</v>
       </c>
       <c r="GR8" t="n">
-        <v>-44.46758620689707</v>
+        <v>532.8499310344828</v>
       </c>
       <c r="GS8" t="n">
-        <v>-5.133517241379323</v>
+        <v>7.928827586206907</v>
       </c>
       <c r="GT8" t="n">
-        <v>-6.321931034482766</v>
+        <v>3.494344827586207</v>
       </c>
       <c r="GU8" t="n">
-        <v>3.86731034482758</v>
+        <v>0.6951724137931095</v>
       </c>
       <c r="GV8" t="n">
-        <v>-32.74482758620691</v>
+        <v>-21.6383448275862</v>
       </c>
       <c r="GW8" t="n">
-        <v>-0.0113103448275873</v>
+        <v>2.424827586206897</v>
       </c>
       <c r="GX8" t="n">
-        <v>-12.69710344827587</v>
+        <v>2.30924137931035</v>
       </c>
       <c r="GY8" t="n">
-        <v>-15.04993103448278</v>
+        <v>20.47503448275863</v>
       </c>
       <c r="GZ8" t="n">
-        <v>-35.28993103448281</v>
+        <v>34.10565517241383</v>
       </c>
       <c r="HA8" t="n">
-        <v>43.02068965517196</v>
+        <v>544.7522758620694</v>
       </c>
       <c r="HB8" t="n">
-        <v>85.38841379310293</v>
+        <v>494.8711724137933</v>
       </c>
       <c r="HC8" t="n">
-        <v>-41.68303448275876</v>
+        <v>54.11533793103456</v>
       </c>
       <c r="HD8" t="n">
-        <v>-0.07493437826541283</v>
+        <v>-0.1526322260115363</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.02603855799373012</v>
+        <v>-0.2251840726323481</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.2890098621684828</v>
+        <v>-0.03688423252488593</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.008583509976612946</v>
+        <v>0.2163840950338227</v>
       </c>
       <c r="HH8" t="n">
-        <v>-0.008865297942796876</v>
+        <v>0.007988646438180536</v>
       </c>
       <c r="HI8" t="n">
-        <v>-0.1920644411051713</v>
+        <v>-0.08783525118736896</v>
       </c>
       <c r="HJ8" t="n">
-        <v>-0.416830344827587</v>
+        <v>0.5411533793103458</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.05363702445496488</v>
+        <v>0.2299829098639041</v>
       </c>
       <c r="HL8" t="n">
-        <v>-0.02167151172544365</v>
+        <v>0.0396535727959671</v>
       </c>
       <c r="HM8" t="n">
-        <v>-0.1484671142674581</v>
+        <v>0.5047517848092564</v>
       </c>
       <c r="HN8" t="n">
-        <v>-0.1920120920541053</v>
+        <v>0.4062730566136419</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.004462153768075516</v>
+        <v>0.004666461630044499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -6268,13 +6268,13 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -6283,10 +6283,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -6298,16 +6298,16 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
@@ -6316,22 +6316,22 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -6358,70 +6358,70 @@
         <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
         <v>1</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
         <v>1</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
         <v>0</v>
@@ -6433,127 +6433,127 @@
         <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.103448275862069</v>
+        <v>3.096551724137931</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.222620689655172</v>
+        <v>4.764689655172414</v>
       </c>
       <c r="BO9" t="n">
-        <v>25.24386206896552</v>
+        <v>45.26455172413793</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.667862068965517</v>
+        <v>14.29406896551724</v>
       </c>
       <c r="BQ9" t="n">
-        <v>117.0885517241379</v>
+        <v>149.4921379310345</v>
       </c>
       <c r="BR9" t="n">
-        <v>31.68910344827586</v>
+        <v>42.28662068965517</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.20496551724138</v>
+        <v>19.65434482758621</v>
       </c>
       <c r="BT9" t="n">
-        <v>40.28275862068966</v>
+        <v>58.96303448275862</v>
       </c>
       <c r="BU9" t="n">
-        <v>1354.574896551724</v>
+        <v>1661.089931034483</v>
       </c>
       <c r="BV9" t="n">
-        <v>48.87641379310345</v>
+        <v>55.38951724137932</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.65020689655172</v>
+        <v>21.44110344827586</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.57958620689655</v>
+        <v>47.05131034482759</v>
       </c>
       <c r="BY9" t="n">
-        <v>80.56551724137931</v>
+        <v>92.31586206896552</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.68551724137931</v>
+        <v>5.955862068965518</v>
       </c>
       <c r="CA9" t="n">
-        <v>20.40993103448276</v>
+        <v>25.01462068965517</v>
       </c>
       <c r="CB9" t="n">
-        <v>45.65379310344827</v>
+        <v>57.17627586206897</v>
       </c>
       <c r="CC9" t="n">
-        <v>172.9473103448276</v>
+        <v>215.0066206896552</v>
       </c>
       <c r="CD9" t="n">
-        <v>1017.273931034483</v>
+        <v>1283.488275862069</v>
       </c>
       <c r="CE9" t="n">
-        <v>778.8</v>
+        <v>970.2099310344828</v>
       </c>
       <c r="CF9" t="n">
-        <v>202.488</v>
+        <v>221.4985103448276</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.3576099027409372</v>
+        <v>0.3502614121510674</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.011315296198055</v>
+        <v>0.934503119868637</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.3746839080459771</v>
+        <v>0.2246509376890502</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.8189989858012171</v>
+        <v>0.7303767695099818</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.1115022829152983</v>
+        <v>0.140773436081507</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.4904317083368588</v>
+        <v>0.5242066611422806</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.02488</v>
+        <v>2.214985103448276</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.225015353037767</v>
+        <v>1.404434217592141</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.1311755543639581</v>
+        <v>0.1773030872222928</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.169841425939701</v>
+        <v>1.490964273839882</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.22430269357164</v>
+        <v>1.497908302535546</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1388317490293456</v>
+        <v>0.1887796520487924</v>
       </c>
       <c r="CS9" t="n">
         <v>1</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -6565,16 +6565,16 @@
         <v>1</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH9" t="n">
         <v>1</v>
@@ -6586,22 +6586,22 @@
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -6622,19 +6622,19 @@
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
@@ -6646,22 +6646,22 @@
         <v>1</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG9" t="n">
         <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
         <v>1</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -6670,28 +6670,28 @@
         <v>1</v>
       </c>
       <c r="EM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ9" t="n">
         <v>1</v>
       </c>
       <c r="ER9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
         <v>1</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU9" t="n">
         <v>1</v>
@@ -6700,22 +6700,22 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX9" t="n">
         <v>1</v>
       </c>
       <c r="EY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
         <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC9" t="n">
         <v>1</v>
@@ -6724,198 +6724,198 @@
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>3.793103448275862</v>
+        <v>3.475862068965517</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.33544827586207</v>
+        <v>1.913379310344828</v>
       </c>
       <c r="FG9" t="n">
-        <v>35.5696551724138</v>
+        <v>42.73213793103449</v>
       </c>
       <c r="FH9" t="n">
-        <v>11.26372413793103</v>
+        <v>11.48027586206897</v>
       </c>
       <c r="FI9" t="n">
-        <v>164.8060689655173</v>
+        <v>176.0308965517242</v>
       </c>
       <c r="FJ9" t="n">
-        <v>30.82703448275862</v>
+        <v>41.45655172413793</v>
       </c>
       <c r="FK9" t="n">
-        <v>19.56331034482758</v>
+        <v>24.87393103448276</v>
       </c>
       <c r="FL9" t="n">
-        <v>48.01903448275862</v>
+        <v>84.18868965517241</v>
       </c>
       <c r="FM9" t="n">
-        <v>1876.892137931035</v>
+        <v>1910.828137931035</v>
       </c>
       <c r="FN9" t="n">
-        <v>49.79751724137932</v>
+        <v>33.80303448275862</v>
       </c>
       <c r="FO9" t="n">
-        <v>24.89875862068966</v>
+        <v>24.87393103448276</v>
       </c>
       <c r="FP9" t="n">
-        <v>39.71944827586207</v>
+        <v>54.21241379310345</v>
       </c>
       <c r="FQ9" t="n">
-        <v>65.80386206896551</v>
+        <v>59.95255172413794</v>
       </c>
       <c r="FR9" t="n">
-        <v>5.33544827586207</v>
+        <v>1.275586206896552</v>
       </c>
       <c r="FS9" t="n">
-        <v>18.97048275862069</v>
+        <v>21.68496551724138</v>
       </c>
       <c r="FT9" t="n">
-        <v>50.39034482758621</v>
+        <v>66.96827586206896</v>
       </c>
       <c r="FU9" t="n">
-        <v>163.0275862068966</v>
+        <v>213.6606896551724</v>
       </c>
       <c r="FV9" t="n">
-        <v>1569.807448275862</v>
+        <v>1593.844965517241</v>
       </c>
       <c r="FW9" t="n">
-        <v>1309.556137931035</v>
+        <v>1273.672827586207</v>
       </c>
       <c r="FX9" t="n">
-        <v>245.7270344827587</v>
+        <v>250.2062344827586</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.4985141065830721</v>
+        <v>0.1674206896551725</v>
       </c>
       <c r="FZ9" t="n">
-        <v>1.014519936204147</v>
+        <v>0.8549241379310346</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.04940229885057471</v>
+        <v>0.428232512315271</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.7338486938349007</v>
+        <v>1.72431921182266</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.08894505357302807</v>
+        <v>0.1791697528405381</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.3160173167728403</v>
+        <v>0.4568841274370655</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.457270344827586</v>
+        <v>2.502062344827586</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.48284865249276</v>
+        <v>1.879063300885442</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.1842667556614572</v>
+        <v>0.1514204177764506</v>
       </c>
       <c r="GH9" t="n">
-        <v>1.640936599296939</v>
+        <v>1.764479890860925</v>
       </c>
       <c r="GI9" t="n">
-        <v>1.606310855987215</v>
+        <v>1.718870042951206</v>
       </c>
       <c r="GJ9" t="n">
-        <v>0.1257598474133188</v>
+        <v>0.2313581728732947</v>
       </c>
       <c r="GK9" t="n">
-        <v>-2.112827586206897</v>
+        <v>2.851310344827586</v>
       </c>
       <c r="GL9" t="n">
-        <v>-10.32579310344828</v>
+        <v>2.532413793103444</v>
       </c>
       <c r="GM9" t="n">
-        <v>-1.595862068965516</v>
+        <v>2.813793103448276</v>
       </c>
       <c r="GN9" t="n">
-        <v>-47.71751724137933</v>
+        <v>-26.53875862068966</v>
       </c>
       <c r="GO9" t="n">
-        <v>0.8620689655172384</v>
+        <v>0.830068965517242</v>
       </c>
       <c r="GP9" t="n">
-        <v>-9.358344827586206</v>
+        <v>-5.219586206896551</v>
       </c>
       <c r="GQ9" t="n">
-        <v>-7.736275862068965</v>
+        <v>-25.22565517241379</v>
       </c>
       <c r="GR9" t="n">
-        <v>-522.3172413793106</v>
+        <v>-249.7382068965519</v>
       </c>
       <c r="GS9" t="n">
-        <v>-0.921103448275872</v>
+        <v>21.5864827586207</v>
       </c>
       <c r="GT9" t="n">
-        <v>-8.248551724137936</v>
+        <v>-3.432827586206894</v>
       </c>
       <c r="GU9" t="n">
-        <v>4.86013793103448</v>
+        <v>-7.16110344827586</v>
       </c>
       <c r="GV9" t="n">
-        <v>14.7616551724138</v>
+        <v>32.36331034482757</v>
       </c>
       <c r="GW9" t="n">
-        <v>-2.649931034482759</v>
+        <v>4.680275862068966</v>
       </c>
       <c r="GX9" t="n">
-        <v>1.439448275862066</v>
+        <v>3.329655172413794</v>
       </c>
       <c r="GY9" t="n">
-        <v>-4.736551724137939</v>
+        <v>-9.791999999999994</v>
       </c>
       <c r="GZ9" t="n">
-        <v>9.919724137931041</v>
+        <v>1.34593103448276</v>
       </c>
       <c r="HA9" t="n">
-        <v>-552.5335172413795</v>
+        <v>-310.3566896551724</v>
       </c>
       <c r="HB9" t="n">
-        <v>-530.7561379310346</v>
+        <v>-303.4628965517242</v>
       </c>
       <c r="HC9" t="n">
-        <v>-43.23903448275865</v>
+        <v>-28.70772413793102</v>
       </c>
       <c r="HD9" t="n">
-        <v>-0.1409042038421349</v>
+        <v>0.1828407224958949</v>
       </c>
       <c r="HE9" t="n">
-        <v>-0.003204640006091886</v>
+        <v>0.07957898193760238</v>
       </c>
       <c r="HF9" t="n">
-        <v>0.3252816091954023</v>
+        <v>-0.2035815746262208</v>
       </c>
       <c r="HG9" t="n">
-        <v>0.0851502919663164</v>
+        <v>-0.9939424423126785</v>
       </c>
       <c r="HH9" t="n">
-        <v>0.0225572293422702</v>
+        <v>-0.03839631675903107</v>
       </c>
       <c r="HI9" t="n">
-        <v>0.1744143915640186</v>
+        <v>0.06732253370521513</v>
       </c>
       <c r="HJ9" t="n">
-        <v>-0.4323903448275863</v>
+        <v>-0.2870772413793103</v>
       </c>
       <c r="HK9" t="n">
-        <v>-0.2578332994549937</v>
+        <v>-0.4746290832933011</v>
       </c>
       <c r="HL9" t="n">
-        <v>-0.05309120129749906</v>
+        <v>0.02588266944584222</v>
       </c>
       <c r="HM9" t="n">
-        <v>-0.4710951733572382</v>
+        <v>-0.2735156170210435</v>
       </c>
       <c r="HN9" t="n">
-        <v>-0.3820081624155756</v>
+        <v>-0.2209617404156605</v>
       </c>
       <c r="HO9" t="n">
-        <v>0.01307190161602673</v>
+        <v>-0.04257852082450234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -6939,10 +6939,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -6957,19 +6957,19 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
         <v>1</v>
@@ -7026,37 +7026,37 @@
         <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -7065,37 +7065,37 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD10" t="n">
         <v>1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
         <v>1</v>
@@ -7104,109 +7104,109 @@
         <v>1</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.517241379310345</v>
+        <v>1.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.00248275862069</v>
+        <v>3.648</v>
       </c>
       <c r="BO10" t="n">
-        <v>27.02234482758621</v>
+        <v>26.144</v>
       </c>
       <c r="BP10" t="n">
-        <v>7.506206896551725</v>
+        <v>6.688000000000001</v>
       </c>
       <c r="BQ10" t="n">
-        <v>111.592275862069</v>
+        <v>134.976</v>
       </c>
       <c r="BR10" t="n">
-        <v>25.52110344827586</v>
+        <v>29.184</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.507034482758622</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.02731034482759</v>
+        <v>51.68</v>
       </c>
       <c r="BU10" t="n">
-        <v>1357.622620689655</v>
+        <v>1698.144</v>
       </c>
       <c r="BV10" t="n">
-        <v>38.03144827586207</v>
+        <v>54.112</v>
       </c>
       <c r="BW10" t="n">
-        <v>20.01655172413793</v>
+        <v>27.36</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.53103448275863</v>
+        <v>51.072</v>
       </c>
       <c r="BY10" t="n">
-        <v>63.05213793103449</v>
+        <v>100.928</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.003310344827587</v>
+        <v>3.04</v>
       </c>
       <c r="CA10" t="n">
-        <v>29.52441379310345</v>
+        <v>24.928</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.02896551724138</v>
+        <v>52.89599999999999</v>
       </c>
       <c r="CC10" t="n">
-        <v>163.1348965517242</v>
+        <v>198.816</v>
       </c>
       <c r="CD10" t="n">
-        <v>1078.391724137931</v>
+        <v>1318.752</v>
       </c>
       <c r="CE10" t="n">
-        <v>842.6968275862071</v>
+        <v>1043.328</v>
       </c>
       <c r="CF10" t="n">
-        <v>189.7068689655173</v>
+        <v>238.1536</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.406288341543514</v>
+        <v>0.3798025974025974</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.8256827586206896</v>
+        <v>0.7426724386724387</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.2849379967159278</v>
+        <v>0.3836190476190476</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.808009414340449</v>
+        <v>1.064</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.08066062579212628</v>
+        <v>0.1200257889907341</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.4303994221400949</v>
+        <v>0.5013286754726944</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.897068689655173</v>
+        <v>2.381536</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.203422561083627</v>
+        <v>1.512421288515406</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.1143664197709674</v>
+        <v>0.1621514547149702</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.114920376793561</v>
+        <v>1.353284231309807</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1.155130390325114</v>
+        <v>1.396026661450469</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1022864158108266</v>
+        <v>0.1418138692218579</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>1</v>
@@ -7218,46 +7218,46 @@
         <v>1</v>
       </c>
       <c r="CX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY10" t="n">
         <v>1</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI10" t="n">
         <v>1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL10" t="n">
         <v>1</v>
@@ -7266,34 +7266,34 @@
         <v>1</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
         <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR10" t="n">
         <v>0</v>
       </c>
       <c r="DS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
         <v>0</v>
@@ -7302,13 +7302,13 @@
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
         <v>0</v>
       </c>
       <c r="EB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="n">
         <v>1</v>
@@ -7317,19 +7317,19 @@
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH10" t="n">
         <v>1</v>
       </c>
       <c r="EI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
         <v>0</v>
@@ -7341,28 +7341,28 @@
         <v>1</v>
       </c>
       <c r="EM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>1</v>
       </c>
       <c r="EO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES10" t="n">
         <v>0</v>
       </c>
       <c r="ET10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="EW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
@@ -7380,208 +7380,208 @@
         <v>1</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA10" t="n">
         <v>1</v>
       </c>
       <c r="FB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD10" t="n">
         <v>1</v>
       </c>
       <c r="FE10" t="n">
-        <v>4.43448275862069</v>
+        <v>3.468965517241379</v>
       </c>
       <c r="FF10" t="n">
-        <v>7.659034482758622</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>45.25793103448276</v>
+        <v>29.21158620689655</v>
       </c>
       <c r="FH10" t="n">
-        <v>17.40689655172414</v>
+        <v>6.985379310344829</v>
       </c>
       <c r="FI10" t="n">
-        <v>206.0976551724138</v>
+        <v>165.1089655172414</v>
       </c>
       <c r="FJ10" t="n">
-        <v>30.63613793103449</v>
+        <v>34.29186206896552</v>
       </c>
       <c r="FK10" t="n">
-        <v>16.71062068965517</v>
+        <v>17.78096551724138</v>
       </c>
       <c r="FL10" t="n">
-        <v>52.22068965517241</v>
+        <v>55.88303448275863</v>
       </c>
       <c r="FM10" t="n">
-        <v>2284.481103448276</v>
+        <v>1780.001655172414</v>
       </c>
       <c r="FN10" t="n">
-        <v>47.34675862068966</v>
+        <v>38.73710344827586</v>
       </c>
       <c r="FO10" t="n">
-        <v>21.58455172413793</v>
+        <v>20.32110344827586</v>
       </c>
       <c r="FP10" t="n">
-        <v>51.52441379310345</v>
+        <v>39.37213793103449</v>
       </c>
       <c r="FQ10" t="n">
-        <v>107.2264827586207</v>
+        <v>59.69324137931035</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.481379310344828</v>
+        <v>4.445241379310345</v>
       </c>
       <c r="FS10" t="n">
-        <v>25.06593103448276</v>
+        <v>37.46703448275863</v>
       </c>
       <c r="FT10" t="n">
-        <v>66.84248275862069</v>
+        <v>52.70786206896553</v>
       </c>
       <c r="FU10" t="n">
-        <v>233.9486896551724</v>
+        <v>208.9263448275862</v>
       </c>
       <c r="FV10" t="n">
-        <v>1864.62675862069</v>
+        <v>1464.389517241379</v>
       </c>
       <c r="FW10" t="n">
-        <v>1544.339862068966</v>
+        <v>1167.193379310345</v>
       </c>
       <c r="FX10" t="n">
-        <v>288.3278344827586</v>
+        <v>247.4094344827586</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7688118687523405</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>1.498185555843632</v>
+        <v>1.101697939653315</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.4490979310344828</v>
+        <v>0.5023828352490421</v>
       </c>
       <c r="GB10" t="n">
-        <v>1.250448150470219</v>
+        <v>0.9333242911877395</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.09034448917054451</v>
+        <v>0.113748879951708</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4439972711494563</v>
+        <v>0.4935439177454735</v>
       </c>
       <c r="GE10" t="n">
-        <v>2.883278344827586</v>
+        <v>2.474094344827587</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.763974953306252</v>
+        <v>1.304299803251528</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1933365402291427</v>
+        <v>0.1620295350204581</v>
       </c>
       <c r="GH10" t="n">
-        <v>2.053580260888411</v>
+        <v>1.650162020422778</v>
       </c>
       <c r="GI10" t="n">
-        <v>1.986785478703033</v>
+        <v>1.596057614538648</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.1192334973204292</v>
+        <v>0.1495617959432159</v>
       </c>
       <c r="GK10" t="n">
-        <v>-4.656551724137932</v>
+        <v>3.648</v>
       </c>
       <c r="GL10" t="n">
-        <v>-18.23558620689655</v>
+        <v>-3.067586206896554</v>
       </c>
       <c r="GM10" t="n">
-        <v>-9.900689655172414</v>
+        <v>-0.2973793103448283</v>
       </c>
       <c r="GN10" t="n">
-        <v>-94.50537931034481</v>
+        <v>-30.13296551724139</v>
       </c>
       <c r="GO10" t="n">
-        <v>-5.115034482758624</v>
+        <v>-5.107862068965524</v>
       </c>
       <c r="GP10" t="n">
-        <v>-8.203586206896551</v>
+        <v>-8.66096551724138</v>
       </c>
       <c r="GQ10" t="n">
-        <v>-19.19337931034482</v>
+        <v>-4.203034482758632</v>
       </c>
       <c r="GR10" t="n">
-        <v>-926.8584827586205</v>
+        <v>-81.85765517241407</v>
       </c>
       <c r="GS10" t="n">
-        <v>-9.315310344827587</v>
+        <v>15.37489655172414</v>
       </c>
       <c r="GT10" t="n">
-        <v>-1.567999999999998</v>
+        <v>7.038896551724136</v>
       </c>
       <c r="GU10" t="n">
-        <v>-13.99337931034482</v>
+        <v>11.69986206896552</v>
       </c>
       <c r="GV10" t="n">
-        <v>-44.1743448275862</v>
+        <v>41.23475862068966</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.5219310344827592</v>
+        <v>-1.405241379310345</v>
       </c>
       <c r="GX10" t="n">
-        <v>4.458482758620693</v>
+        <v>-12.53903448275863</v>
       </c>
       <c r="GY10" t="n">
-        <v>-31.81351724137931</v>
+        <v>0.1881379310344684</v>
       </c>
       <c r="GZ10" t="n">
-        <v>-70.81379310344826</v>
+        <v>-10.11034482758618</v>
       </c>
       <c r="HA10" t="n">
-        <v>-786.2350344827587</v>
+        <v>-145.6375172413793</v>
       </c>
       <c r="HB10" t="n">
-        <v>-701.6430344827586</v>
+        <v>-123.8653793103449</v>
       </c>
       <c r="HC10" t="n">
-        <v>-98.62096551724136</v>
+        <v>-9.255834482758587</v>
       </c>
       <c r="HD10" t="n">
-        <v>-0.3625235272088265</v>
+        <v>0.3798025974025974</v>
       </c>
       <c r="HE10" t="n">
-        <v>-0.6725027972229425</v>
+        <v>-0.3590255009808762</v>
       </c>
       <c r="HF10" t="n">
-        <v>-0.164159934318555</v>
+        <v>-0.1187637876299945</v>
       </c>
       <c r="HG10" t="n">
-        <v>-0.4424387361297704</v>
+        <v>0.1306757088122603</v>
       </c>
       <c r="HH10" t="n">
-        <v>-0.009683863378418228</v>
+        <v>0.006276909039026071</v>
       </c>
       <c r="HI10" t="n">
-        <v>-0.01359784900936134</v>
+        <v>0.007784757727220926</v>
       </c>
       <c r="HJ10" t="n">
-        <v>-0.9862096551724138</v>
+        <v>-0.0925583448275864</v>
       </c>
       <c r="HK10" t="n">
-        <v>-0.5605523922226252</v>
+        <v>0.2081214852638786</v>
       </c>
       <c r="HL10" t="n">
-        <v>-0.07897012045817529</v>
+        <v>0.0001219196945120293</v>
       </c>
       <c r="HM10" t="n">
-        <v>-0.9386598840948503</v>
+        <v>-0.296877789112971</v>
       </c>
       <c r="HN10" t="n">
-        <v>-0.831655088377919</v>
+        <v>-0.2000309530881792</v>
       </c>
       <c r="HO10" t="n">
-        <v>-0.01694708150960264</v>
+        <v>-0.007747926721358073</v>
       </c>
     </row>
     <row r="11">
@@ -7589,13 +7589,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -7619,22 +7619,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -7658,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -7673,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -7682,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -7694,34 +7694,34 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -7730,10 +7730,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -7742,16 +7742,16 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC11" t="n">
         <v>1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
         <v>1</v>
@@ -7763,496 +7763,496 @@
         <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
+        <v>4.427586206896552</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.345103448275863</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>43.83889655172413</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>11.53655172413793</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>155.1666206896552</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>30.57186206896552</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>17.3048275862069</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>55.37544827586207</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1750.094896551724</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>43.26206896551724</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>15.57434482758621</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>34.0328275862069</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>55.95227586206896</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>2.884137931034483</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>13.26703448275862</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>49.03034482758621</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>148.8215172413793</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>1434.570206896552</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1206.146482758621</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>238.4028413793103</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.3920612193903049</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.736253714052065</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.146495894909688</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.8482611733094492</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.1110739925973439</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.3335457013861843</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.384028413793104</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.549831417624521</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.1421824494041312</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>1.549804530975228</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1.536491906323615</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.1479239038857002</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
         <v>4.062068965517241</v>
       </c>
-      <c r="BN11" t="n">
-        <v>5.878620689655173</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>39.97462068965518</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>11.75724137931035</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>171.655724137931</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>23.51448275862069</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>13.5208275862069</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>40.5624827586207</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>2051.05075862069</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>44.08965517241379</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>24.69020689655173</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>29.39310344827586</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>56.43475862068966</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1.175724137931035</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>18.81158620689655</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>51.73186206896553</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>152.8441379310345</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>1730.078068965517</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>1501.987586206897</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>254.7794206896552</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>0.4145974591651543</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>0.9075765275257107</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>0.2783437826541275</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>1.044174584036653</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>0.07007663856985839</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>0.2626341926944465</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.547794206896552</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>1.596156716446972</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>0.1677386832216946</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.716249920023531</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>1.671584160084428</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>0.09344089162318693</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER11" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES11" t="n">
-        <v>1</v>
-      </c>
-      <c r="ET11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY11" t="n">
-        <v>1</v>
-      </c>
-      <c r="EZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="FB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="FD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE11" t="n">
-        <v>3.006896551724138</v>
-      </c>
       <c r="FF11" t="n">
-        <v>4.109793103448276</v>
+        <v>5.842758620689655</v>
       </c>
       <c r="FG11" t="n">
-        <v>58.22206896551724</v>
+        <v>40.31503448275862</v>
       </c>
       <c r="FH11" t="n">
-        <v>17.12413793103448</v>
+        <v>12.26979310344828</v>
       </c>
       <c r="FI11" t="n">
-        <v>198.64</v>
+        <v>164.1815172413793</v>
       </c>
       <c r="FJ11" t="n">
-        <v>36.3031724137931</v>
+        <v>23.95531034482758</v>
       </c>
       <c r="FK11" t="n">
-        <v>15.06924137931034</v>
+        <v>12.85406896551724</v>
       </c>
       <c r="FL11" t="n">
-        <v>56.85213793103448</v>
+        <v>37.39365517241379</v>
       </c>
       <c r="FM11" t="n">
-        <v>2196.684413793103</v>
+        <v>1948.56</v>
       </c>
       <c r="FN11" t="n">
-        <v>67.12662068965517</v>
+        <v>46.74206896551724</v>
       </c>
       <c r="FO11" t="n">
-        <v>15.75420689655172</v>
+        <v>26.29241379310345</v>
       </c>
       <c r="FP11" t="n">
-        <v>67.12662068965517</v>
+        <v>37.39365517241379</v>
       </c>
       <c r="FQ11" t="n">
-        <v>71.92137931034482</v>
+        <v>62.51751724137931</v>
       </c>
       <c r="FR11" t="n">
-        <v>6.849655172413793</v>
+        <v>1.168551724137931</v>
       </c>
       <c r="FS11" t="n">
-        <v>23.97379310344828</v>
+        <v>20.44965517241379</v>
       </c>
       <c r="FT11" t="n">
-        <v>60.96193103448276</v>
+        <v>57.84331034482759</v>
       </c>
       <c r="FU11" t="n">
-        <v>248.6424827586207</v>
+        <v>160.6758620689655</v>
       </c>
       <c r="FV11" t="n">
-        <v>1817.898482758621</v>
+        <v>1616.107034482759</v>
       </c>
       <c r="FW11" t="n">
-        <v>1489.8</v>
+        <v>1379.475310344827</v>
       </c>
       <c r="FX11" t="n">
-        <v>279.8769103448276</v>
+        <v>248.6678068965517</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.2131003831417624</v>
+        <v>0.4008321652938713</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.001087481713689</v>
+        <v>0.9282574340360186</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.4193883664228492</v>
+        <v>0.2036112852664577</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.029843260188088</v>
+        <v>0.9891150229081264</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.1064678293850757</v>
+        <v>0.06578249405180323</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.4807371503705555</v>
+        <v>0.2977602343205121</v>
       </c>
       <c r="GE11" t="n">
-        <v>2.798769103448276</v>
+        <v>2.486678068965517</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.937448606815086</v>
+        <v>1.736609519870606</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.2222491065042421</v>
+        <v>0.1729659018656966</v>
       </c>
       <c r="GH11" t="n">
-        <v>1.986958019306919</v>
+        <v>1.639551385460649</v>
       </c>
       <c r="GI11" t="n">
-        <v>1.926699162415045</v>
+        <v>1.609237089600277</v>
       </c>
       <c r="GJ11" t="n">
-        <v>0.1355170579494983</v>
+        <v>0.08878929200502401</v>
       </c>
       <c r="GK11" t="n">
-        <v>1.768827586206897</v>
+        <v>0.5023448275862075</v>
       </c>
       <c r="GL11" t="n">
-        <v>-18.24744827586206</v>
+        <v>3.523862068965514</v>
       </c>
       <c r="GM11" t="n">
-        <v>-5.366896551724137</v>
+        <v>-0.7332413793103445</v>
       </c>
       <c r="GN11" t="n">
-        <v>-26.98427586206896</v>
+        <v>-9.014896551724149</v>
       </c>
       <c r="GO11" t="n">
-        <v>-12.78868965517241</v>
+        <v>6.616551724137931</v>
       </c>
       <c r="GP11" t="n">
-        <v>-1.548413793103448</v>
+        <v>4.450758620689655</v>
       </c>
       <c r="GQ11" t="n">
-        <v>-16.28965517241379</v>
+        <v>17.98179310344828</v>
       </c>
       <c r="GR11" t="n">
-        <v>-145.6336551724139</v>
+        <v>-198.4651034482758</v>
       </c>
       <c r="GS11" t="n">
-        <v>-23.03696551724138</v>
+        <v>-3.479999999999997</v>
       </c>
       <c r="GT11" t="n">
-        <v>8.936000000000003</v>
+        <v>-10.71806896551724</v>
       </c>
       <c r="GU11" t="n">
-        <v>-37.7335172413793</v>
+        <v>-3.360827586206895</v>
       </c>
       <c r="GV11" t="n">
-        <v>-15.48662068965516</v>
+        <v>-6.565241379310351</v>
       </c>
       <c r="GW11" t="n">
-        <v>-5.673931034482758</v>
+        <v>1.715586206896552</v>
       </c>
       <c r="GX11" t="n">
-        <v>-5.162206896551723</v>
+        <v>-7.182620689655172</v>
       </c>
       <c r="GY11" t="n">
-        <v>-9.230068965517233</v>
+        <v>-8.812965517241381</v>
       </c>
       <c r="GZ11" t="n">
-        <v>-95.79834482758619</v>
+        <v>-11.8543448275862</v>
       </c>
       <c r="HA11" t="n">
-        <v>-87.82041379310317</v>
+        <v>-181.536827586207</v>
       </c>
       <c r="HB11" t="n">
-        <v>12.18758620689664</v>
+        <v>-173.3288275862067</v>
       </c>
       <c r="HC11" t="n">
-        <v>-25.09748965517244</v>
+        <v>-10.26496551724139</v>
       </c>
       <c r="HD11" t="n">
-        <v>0.2014970760233918</v>
+        <v>-0.008770945903566474</v>
       </c>
       <c r="HE11" t="n">
-        <v>-0.09351095418797783</v>
+        <v>-0.1920037199839536</v>
       </c>
       <c r="HF11" t="n">
-        <v>-0.1410445837687217</v>
+        <v>-0.05711539035676969</v>
       </c>
       <c r="HG11" t="n">
-        <v>0.01433132384856517</v>
+        <v>-0.1408538495986772</v>
       </c>
       <c r="HH11" t="n">
-        <v>-0.03639119081521731</v>
+        <v>0.04529149854554065</v>
       </c>
       <c r="HI11" t="n">
-        <v>-0.218102957676109</v>
+        <v>0.03578546706567226</v>
       </c>
       <c r="HJ11" t="n">
-        <v>-0.2509748965517242</v>
+        <v>-0.1026496551724136</v>
       </c>
       <c r="HK11" t="n">
-        <v>-0.3412918903681144</v>
+        <v>-0.1867781022460855</v>
       </c>
       <c r="HL11" t="n">
-        <v>-0.05451042328254749</v>
+        <v>-0.03078345246156541</v>
       </c>
       <c r="HM11" t="n">
-        <v>-0.2707080992833875</v>
+        <v>-0.08974685448542119</v>
       </c>
       <c r="HN11" t="n">
-        <v>-0.2551150023306168</v>
+        <v>-0.07274518327666168</v>
       </c>
       <c r="HO11" t="n">
-        <v>-0.04207616632631138</v>
+        <v>0.05913461188067622</v>
       </c>
     </row>
   </sheetData>
